--- a/AFM/MechsysLU_AFM.xlsx
+++ b/AFM/MechsysLU_AFM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\heinr\OneDrive\Documents\TU\Mechatronische Systeme Labor\AFM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\7_TU\Master Automatisierung und Robotische Systeme\Mechatronische Systeme Labor\AFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38EF3E7F-F453-4240-A954-18ADCCA5B182}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B54F4B2-102D-410C-BE7F-31807E6811B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="11520" windowHeight="12360" xr2:uid="{B84AB7BC-A147-41D7-A40F-EB74A04C0736}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B84AB7BC-A147-41D7-A40F-EB74A04C0736}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="68">
   <si>
     <t>V</t>
   </si>
@@ -231,6 +231,15 @@
   </si>
   <si>
     <t>scope_14</t>
+  </si>
+  <si>
+    <t>avg height</t>
+  </si>
+  <si>
+    <t>1/2piRC=</t>
+  </si>
+  <si>
+    <t>step</t>
   </si>
 </sst>
 </file>
@@ -302,6 +311,39 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Measured</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> Cantilever H</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>eight</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -794,7 +836,418 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="de-DE"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Tabelle1!$I$38</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>100um</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Tabelle1!$I$39:$I$44</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>78</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4555-4291-9E22-5D3BD5654799}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Tabelle1!$J$38</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>250um</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Tabelle1!$J$39:$J$44</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>220</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>295</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>370</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-4555-4291-9E22-5D3BD5654799}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1034222495"/>
+        <c:axId val="1034224895"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1034222495"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1034224895"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1034224895"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1034222495"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="de-DE"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.7" r="0.7" t="0.78740157499999996" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -1337,20 +1790,536 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>464820</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>118110</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>655320</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>127635</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>281940</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>118110</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>472440</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>127635</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1370,6 +2339,245 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>666750</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3" name="Rechteck 2">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7D5F5A13-BBB6-C0AD-482A-4F7996D62E7F}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="6762750" y="1352550"/>
+              <a:ext cx="1066800" cy="371475"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="accent2"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:r>
+                      <a:rPr lang="de-DE" sz="1100" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                        <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>≈</m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="de-AT" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                        <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>0.27 </m:t>
+                    </m:r>
+                    <m:f>
+                      <m:fPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="de-AT" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:fPr>
+                      <m:num>
+                        <m:r>
+                          <m:rPr>
+                            <m:nor/>
+                          </m:rPr>
+                          <a:rPr lang="de-AT" sz="1100" b="0" i="0">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>mm</m:t>
+                        </m:r>
+                      </m:num>
+                      <m:den>
+                        <m:r>
+                          <a:rPr lang="de-AT" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>100</m:t>
+                        </m:r>
+                        <m:r>
+                          <m:rPr>
+                            <m:nor/>
+                          </m:rPr>
+                          <a:rPr lang="de-AT" sz="1100" b="0" i="0">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t> </m:t>
+                        </m:r>
+                        <m:r>
+                          <m:rPr>
+                            <m:nor/>
+                          </m:rPr>
+                          <a:rPr lang="de-AT" sz="1100" b="0" i="0">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>mV</m:t>
+                        </m:r>
+                      </m:den>
+                    </m:f>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="de-DE" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3" name="Rechteck 2">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7D5F5A13-BBB6-C0AD-482A-4F7996D62E7F}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="6762750" y="1352550"/>
+              <a:ext cx="1066800" cy="371475"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="accent2"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr lang="de-DE" sz="1100" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>≈</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="de-AT" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>0.27  "mm" /100" mV" </a:t>
+              </a:r>
+              <a:endParaRPr lang="de-DE" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>461962</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>100012</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>461962</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>176212</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Diagramm 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{30B57B97-D298-68CF-ECA0-B057EF908556}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1695,15 +2903,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAC21238-07F0-4F79-A400-2B4B4E09B5E3}">
-  <dimension ref="A1:D67"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:J67"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1713,8 +2921,11 @@
       <c r="C2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>-0.5</v>
       </c>
@@ -1724,8 +2935,12 @@
       <c r="C3">
         <v>45.7</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D3">
+        <f>(B13-B3)/(A13-A3)</f>
+        <v>2.7000000000000011</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>-0.4</v>
       </c>
@@ -1733,7 +2948,7 @@
         <v>11.3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>-0.3</v>
       </c>
@@ -1741,7 +2956,7 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>-0.2</v>
       </c>
@@ -1749,7 +2964,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>-0.1</v>
       </c>
@@ -1757,7 +2972,7 @@
         <v>12.05</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>0</v>
       </c>
@@ -1765,7 +2980,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>0.1</v>
       </c>
@@ -1773,7 +2988,7 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>0.2</v>
       </c>
@@ -1781,7 +2996,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>0.3</v>
       </c>
@@ -1789,7 +3004,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>0.4</v>
       </c>
@@ -1797,7 +3012,7 @@
         <v>13.6</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>0.5</v>
       </c>
@@ -1805,22 +3020,22 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>3</v>
       </c>
@@ -1828,7 +3043,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>5</v>
       </c>
@@ -1836,25 +3051,28 @@
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>12</v>
       </c>
       <c r="D26" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E26" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>13</v>
       </c>
@@ -1862,13 +3080,17 @@
         <f>1/(220000*100*10^-9)</f>
         <v>45.454545454545453</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E27">
+        <f>1/(2*PI()*220000*100*10^-9)</f>
+        <v>7.2343155950861515</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>14</v>
       </c>
@@ -1876,7 +3098,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>16</v>
       </c>
@@ -1884,7 +3106,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>20</v>
       </c>
@@ -1892,7 +3114,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>18</v>
       </c>
@@ -1900,7 +3122,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>22</v>
       </c>
@@ -1908,7 +3130,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>25</v>
       </c>
@@ -1916,49 +3138,172 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I38" t="s">
+        <v>30</v>
+      </c>
+      <c r="J38" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E39">
+        <v>0</v>
+      </c>
+      <c r="F39">
+        <v>-70</v>
+      </c>
+      <c r="G39">
+        <v>-275</v>
+      </c>
+      <c r="I39">
+        <f>F39-$F$39</f>
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <f>G39-$G$39</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>29</v>
       </c>
       <c r="B40" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E40">
+        <v>1</v>
+      </c>
+      <c r="F40">
+        <v>-50</v>
+      </c>
+      <c r="G40">
+        <v>-210</v>
+      </c>
+      <c r="I40">
+        <f t="shared" ref="I40:J44" si="0">F40-$F$39</f>
+        <v>20</v>
+      </c>
+      <c r="J40">
+        <f t="shared" ref="J40:J44" si="1">G40-$G$39</f>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>31</v>
       </c>
       <c r="B41" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E41">
+        <v>2</v>
+      </c>
+      <c r="F41">
+        <v>-35</v>
+      </c>
+      <c r="G41">
+        <v>-125</v>
+      </c>
+      <c r="I41">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="J41">
+        <f t="shared" si="1"/>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>33</v>
       </c>
       <c r="B42" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E42">
+        <v>3</v>
+      </c>
+      <c r="F42">
+        <v>-30</v>
+      </c>
+      <c r="G42">
+        <v>-55</v>
+      </c>
+      <c r="I42">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="J42">
+        <f t="shared" si="1"/>
+        <v>220</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E43">
+        <v>4</v>
+      </c>
+      <c r="F43">
+        <v>-15</v>
+      </c>
+      <c r="G43">
+        <v>20</v>
+      </c>
+      <c r="I43">
+        <f t="shared" si="0"/>
+        <v>55</v>
+      </c>
+      <c r="J43">
+        <f t="shared" si="1"/>
+        <v>295</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E44">
+        <v>5</v>
+      </c>
+      <c r="F44">
+        <v>8</v>
+      </c>
+      <c r="G44">
+        <v>95</v>
+      </c>
+      <c r="I44">
+        <f t="shared" si="0"/>
+        <v>78</v>
+      </c>
+      <c r="J44">
+        <f t="shared" si="1"/>
+        <v>370</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>36</v>
       </c>
       <c r="B45" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E45" t="s">
+        <v>67</v>
+      </c>
+      <c r="F45">
+        <f>(F44-F39)/5</f>
+        <v>15.6</v>
+      </c>
+      <c r="G45">
+        <f>(G44-G39)/5</f>
+        <v>74</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>38</v>
       </c>
@@ -1966,7 +3311,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>40</v>
       </c>
@@ -1974,22 +3319,22 @@
         <v>41</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>45</v>
       </c>
@@ -1997,7 +3342,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>47</v>
       </c>
@@ -2005,7 +3350,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>48</v>
       </c>
@@ -2019,7 +3364,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>49</v>
       </c>
@@ -2033,12 +3378,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>55</v>
       </c>
@@ -2052,7 +3397,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>56</v>
       </c>
@@ -2060,12 +3405,12 @@
         <v>57</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>62</v>
       </c>
@@ -2073,7 +3418,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>63</v>
       </c>
@@ -2081,7 +3426,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>64</v>
       </c>

--- a/AFM/MechsysLU_AFM.xlsx
+++ b/AFM/MechsysLU_AFM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\7_TU\Master Automatisierung und Robotische Systeme\Mechatronische Systeme Labor\AFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B54F4B2-102D-410C-BE7F-31807E6811B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9B8A663-E698-4C10-8509-8BB15CA6B18B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B84AB7BC-A147-41D7-A40F-EB74A04C0736}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B84AB7BC-A147-41D7-A40F-EB74A04C0736}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="81">
   <si>
     <t>V</t>
   </si>
@@ -241,6 +241,45 @@
   <si>
     <t>step</t>
   </si>
+  <si>
+    <t>100 µm</t>
+  </si>
+  <si>
+    <t>250 µm</t>
+  </si>
+  <si>
+    <t>Average</t>
+  </si>
+  <si>
+    <t>readout</t>
+  </si>
+  <si>
+    <t>avg</t>
+  </si>
+  <si>
+    <t>norm</t>
+  </si>
+  <si>
+    <t>delta (100 µm)</t>
+  </si>
+  <si>
+    <t>weighted</t>
+  </si>
+  <si>
+    <t>weights</t>
+  </si>
+  <si>
+    <t>w avg</t>
+  </si>
+  <si>
+    <t>slow scan</t>
+  </si>
+  <si>
+    <t>fast scan</t>
+  </si>
+  <si>
+    <t>assumed height</t>
+  </si>
 </sst>
 </file>
 
@@ -275,10 +314,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -317,7 +357,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -330,15 +370,15 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US"/>
+              <a:rPr lang="en-US" b="1"/>
               <a:t>Measured</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="en-US" baseline="0"/>
+              <a:rPr lang="en-US" b="1" baseline="0"/>
               <a:t> Cantilever H</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="en-US"/>
+              <a:rPr lang="en-US" b="1"/>
               <a:t>eight</a:t>
             </a:r>
           </a:p>
@@ -357,7 +397,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -375,7 +415,17 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="9.9852817876932051E-2"/>
+          <c:y val="0.16484444444444443"/>
+          <c:w val="0.86831847841936427"/>
+          <c:h val="0.53649588801399828"/>
+        </c:manualLayout>
+      </c:layout>
       <c:lineChart>
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
@@ -549,7 +599,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -562,7 +612,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="de-AT"/>
+                  <a:rPr lang="de-AT" b="1"/>
                   <a:t>V</a:t>
                 </a:r>
               </a:p>
@@ -581,7 +631,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65000"/>
@@ -666,11 +716,11 @@
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -683,12 +733,20 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="de-AT"/>
+                  <a:rPr lang="de-AT" b="1"/>
                   <a:t>mm</a:t>
                 </a:r>
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="3.4722222222222224E-2"/>
+              <c:y val="6.5969903762029769E-2"/>
+            </c:manualLayout>
+          </c:layout>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -698,11 +756,11 @@
             <a:effectLst/>
           </c:spPr>
           <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65000"/>
@@ -851,6 +909,43 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="de-DE" b="1"/>
+              <a:t>AFM</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="de-DE" b="1" baseline="0"/>
+              <a:t> Readout Voltage and Height</a:t>
+            </a:r>
+            <a:br>
+              <a:rPr lang="de-DE" b="1" baseline="0"/>
+            </a:br>
+            <a:r>
+              <a:rPr lang="de-DE" b="1" baseline="0"/>
+              <a:t>(slow scan)</a:t>
+            </a:r>
+            <a:endParaRPr lang="de-DE" b="1"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -864,7 +959,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -882,26 +977,36 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="9.1358477343806532E-2"/>
+          <c:y val="0.225777111031049"/>
+          <c:w val="0.67090229671536605"/>
+          <c:h val="0.58952026391620516"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Tabelle1!$I$38</c:f>
+              <c:f>Tabelle1!$I$48</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>100um</c:v>
+                  <c:v>100 µm</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln w="19050" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
@@ -910,11 +1015,23 @@
             <a:effectLst/>
           </c:spPr>
           <c:marker>
-            <c:symbol val="none"/>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
           </c:marker>
-          <c:val>
+          <c:xVal>
             <c:numRef>
-              <c:f>Tabelle1!$I$39:$I$44</c:f>
+              <c:f>Tabelle1!$I$49:$I$54</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -922,27 +1039,54 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>20</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>35</c:v>
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>500</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Tabelle1!$J$49:$J$54</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>36</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>40</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>55</c:v>
+                  <c:v>54</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>78</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:val>
+          </c:yVal>
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-4555-4291-9E22-5D3BD5654799}"/>
+              <c16:uniqueId val="{00000000-B168-4806-9DB1-84053C6C9B43}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -951,17 +1095,17 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Tabelle1!$J$38</c:f>
+              <c:f>Tabelle1!$I$56</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>250um</c:v>
+                  <c:v>250 µm</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln w="19050" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent2"/>
               </a:solidFill>
@@ -970,11 +1114,23 @@
             <a:effectLst/>
           </c:spPr>
           <c:marker>
-            <c:symbol val="none"/>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
           </c:marker>
-          <c:val>
+          <c:xVal>
             <c:numRef>
-              <c:f>Tabelle1!$J$39:$J$44</c:f>
+              <c:f>Tabelle1!$I$57:$I$62</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -982,27 +1138,217 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>65</c:v>
+                  <c:v>250</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>150</c:v>
+                  <c:v>500</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>220</c:v>
+                  <c:v>750</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>295</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>370</c:v>
+                  <c:v>1250</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:val>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Tabelle1!$J$57:$J$62</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>135</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>215</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>285</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>355</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-4555-4291-9E22-5D3BD5654799}"/>
+              <c16:uniqueId val="{00000001-B168-4806-9DB1-84053C6C9B43}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Tabelle1!$I$64</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Average</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="12700" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Tabelle1!$I$65:$I$66</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1500</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Tabelle1!$J$65:$J$66</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>371.14285714285717</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-B168-4806-9DB1-84053C6C9B43}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Tabelle1!$I$68</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>???</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Tabelle1!$I$69:$I$74</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>525.40415704387988</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>80.831408775981515</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>687.06697459584291</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>40.415704387990758</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Tabelle1!$J$69:$J$74</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>130</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-B168-4806-9DB1-84053C6C9B43}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1014,17 +1360,3312 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:smooth val="0"/>
-        <c:axId val="1034222495"/>
-        <c:axId val="1034224895"/>
-      </c:lineChart>
+        <c:axId val="1026746751"/>
+        <c:axId val="1026745311"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1026746751"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1500"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="5000"/>
+                  <a:lumOff val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="de-DE" b="1"/>
+                  <a:t>Height (µm)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="de-DE"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="in"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1026745311"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="250"/>
+        <c:minorUnit val="50"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1026745311"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="5000"/>
+                  <a:lumOff val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="de-DE" b="1"/>
+                  <a:t>Voltage (mV)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="3.0974073643502232E-2"/>
+              <c:y val="0.12214557259828444"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="de-DE"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1026746751"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="100"/>
+        <c:minorUnit val="20"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="de-DE"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.7" r="0.7" t="0.78740157499999996" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="de-DE"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="de-DE" b="1"/>
+              <a:t>AFM</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="de-DE" b="1" baseline="0"/>
+              <a:t> Readout Voltage and Height</a:t>
+            </a:r>
+            <a:br>
+              <a:rPr lang="de-DE" b="1" baseline="0"/>
+            </a:br>
+            <a:r>
+              <a:rPr lang="de-DE" b="1" baseline="0"/>
+              <a:t>(slow scan)</a:t>
+            </a:r>
+            <a:endParaRPr lang="de-DE" b="1"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.10426434136193247"/>
+          <c:y val="0.225777111031049"/>
+          <c:w val="0.68100768986253524"/>
+          <c:h val="0.58952026391620516"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Tabelle1!$I$48</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>100 µm</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Tabelle1!$I$49:$I$54</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>500</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Tabelle1!$J$49:$J$54</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>54</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>78</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-A360-44EE-9FC4-09E762D509E9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Tabelle1!$I$56</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>250 µm</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Tabelle1!$I$57:$I$62</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>750</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1250</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Tabelle1!$J$57:$J$62</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>135</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>215</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>285</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>355</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-A360-44EE-9FC4-09E762D509E9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1026746751"/>
+        <c:axId val="1026745311"/>
+        <c:extLst>
+          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+            <c15:filteredScatterSeries>
+              <c15:ser>
+                <c:idx val="2"/>
+                <c:order val="2"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Tabelle1!$I$64</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>Average</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="12700" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent4"/>
+                    </a:solidFill>
+                    <a:prstDash val="dash"/>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="none"/>
+                </c:marker>
+                <c:xVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Tabelle1!$I$65:$I$66</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="2"/>
+                      <c:pt idx="0">
+                        <c:v>0</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>1500</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:xVal>
+                <c:yVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Tabelle1!$J$65:$J$66</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="2"/>
+                      <c:pt idx="0">
+                        <c:v>0</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>371.14285714285717</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:yVal>
+                <c:smooth val="0"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000002-A360-44EE-9FC4-09E762D509E9}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredScatterSeries>
+            <c15:filteredScatterSeries>
+              <c15:ser>
+                <c:idx val="3"/>
+                <c:order val="3"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Tabelle1!$I$68</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>???</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="19050" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent4"/>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent4"/>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent4"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:xVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Tabelle1!$I$69:$I$74</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>0</c:formatCode>
+                      <c:ptCount val="6"/>
+                      <c:pt idx="0" formatCode="General">
+                        <c:v>0</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>525.40415704387988</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>0</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>80.831408775981515</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>687.06697459584291</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>40.415704387990758</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:xVal>
+                <c:yVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Tabelle1!$J$69:$J$74</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="6"/>
+                      <c:pt idx="0">
+                        <c:v>0</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>130</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>0</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>20</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>170</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>10</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:yVal>
+                <c:smooth val="0"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000003-A360-44EE-9FC4-09E762D509E9}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredScatterSeries>
+          </c:ext>
+        </c:extLst>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1026746751"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1500"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="5000"/>
+                  <a:lumOff val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="de-DE" b="1"/>
+                  <a:t>Height (µm)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="de-DE"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="in"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1026745311"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="250"/>
+        <c:minorUnit val="50"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1026745311"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="5000"/>
+                  <a:lumOff val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="de-DE" b="1"/>
+                  <a:t>Voltage (mV)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="3.8717592054377789E-2"/>
+              <c:y val="0.11797840554344781"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="de-DE"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1026746751"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="100"/>
+        <c:minorUnit val="20"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="de-DE"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.7" r="0.7" t="0.78740157499999996" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="de-DE"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="de-DE" b="1"/>
+              <a:t>AFM</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="de-DE" b="1" baseline="0"/>
+              <a:t> Readout Voltage and Height</a:t>
+            </a:r>
+            <a:br>
+              <a:rPr lang="de-DE" b="1" baseline="0"/>
+            </a:br>
+            <a:r>
+              <a:rPr lang="de-DE" b="1" baseline="0"/>
+              <a:t>(fast scan)</a:t>
+            </a:r>
+            <a:endParaRPr lang="de-DE" b="1"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.11458903257643323"/>
+          <c:y val="0.225777111031049"/>
+          <c:w val="0.64767174148273943"/>
+          <c:h val="0.58952026391620516"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Tabelle1!$Z$47</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>100 µm</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Tabelle1!$Z$48:$Z$53</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>500</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Tabelle1!$AA$48:$AA$53</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>75</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2605-4D74-89CE-1616A1F76A62}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Tabelle1!$Z$55</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>250 µm</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Tabelle1!$Z$56:$Z$61</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>750</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1250</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Tabelle1!$AA$56:$AA$61</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>135</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>215</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>285</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>365</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-2605-4D74-89CE-1616A1F76A62}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Tabelle1!$I$64</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Average</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="12700" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Tabelle1!$I$65:$I$66</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1500</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Tabelle1!$J$65:$J$66</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>371.14285714285717</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-2605-4D74-89CE-1616A1F76A62}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Tabelle1!$I$68</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>???</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Tabelle1!$I$69:$I$74</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>525.40415704387988</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>80.831408775981515</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>687.06697459584291</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>40.415704387990758</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Tabelle1!$J$69:$J$74</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>130</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-2605-4D74-89CE-1616A1F76A62}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1026746751"/>
+        <c:axId val="1026745311"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1026746751"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1500"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="5000"/>
+                  <a:lumOff val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="de-DE" b="1"/>
+                  <a:t>Height (µm)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="de-DE"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="in"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1026745311"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="250"/>
+        <c:minorUnit val="50"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1026745311"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="5000"/>
+                  <a:lumOff val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="de-DE" b="1"/>
+                  <a:t>Voltage (mV)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="2.5811728036251862E-2"/>
+              <c:y val="0.12631273965312106"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="de-DE"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1026746751"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="100"/>
+        <c:minorUnit val="20"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="de-DE"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.7" r="0.7" t="0.78740157499999996" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="de-DE"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="de-DE" b="1"/>
+              <a:t>AFM</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="de-DE" b="1" baseline="0"/>
+              <a:t> Readout Voltage and Height</a:t>
+            </a:r>
+            <a:br>
+              <a:rPr lang="de-DE" b="1" baseline="0"/>
+            </a:br>
+            <a:r>
+              <a:rPr lang="de-DE" b="1" baseline="0"/>
+              <a:t>(fast scan)</a:t>
+            </a:r>
+            <a:endParaRPr lang="de-DE" b="1"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="9.1358477343806532E-2"/>
+          <c:y val="0.225777111031049"/>
+          <c:w val="0.69391355388066134"/>
+          <c:h val="0.58952026391620516"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Tabelle1!$Z$47</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>100 µm</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Tabelle1!$Z$48:$Z$53</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>500</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Tabelle1!$AA$48:$AA$53</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>75</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-D15F-4363-97C5-9CF82FC49F12}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Tabelle1!$Z$55</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>250 µm</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Tabelle1!$Z$56:$Z$61</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>750</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1250</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Tabelle1!$AA$56:$AA$61</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>135</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>215</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>285</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>365</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-D15F-4363-97C5-9CF82FC49F12}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1026746751"/>
+        <c:axId val="1026745311"/>
+        <c:extLst>
+          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+            <c15:filteredScatterSeries>
+              <c15:ser>
+                <c:idx val="2"/>
+                <c:order val="2"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Tabelle1!$I$64</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>Average</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="12700" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent4"/>
+                    </a:solidFill>
+                    <a:prstDash val="dash"/>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent3"/>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent3"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:xVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Tabelle1!$I$65:$I$66</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="2"/>
+                      <c:pt idx="0">
+                        <c:v>0</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>1500</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:xVal>
+                <c:yVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Tabelle1!$J$65:$J$66</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="2"/>
+                      <c:pt idx="0">
+                        <c:v>0</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>371.14285714285717</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:yVal>
+                <c:smooth val="0"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000002-D15F-4363-97C5-9CF82FC49F12}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredScatterSeries>
+            <c15:filteredScatterSeries>
+              <c15:ser>
+                <c:idx val="3"/>
+                <c:order val="3"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Tabelle1!$I$68</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>???</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="19050" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent4"/>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent4"/>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent4"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:xVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Tabelle1!$I$69:$I$74</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>0</c:formatCode>
+                      <c:ptCount val="6"/>
+                      <c:pt idx="0" formatCode="General">
+                        <c:v>0</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>525.40415704387988</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>0</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>80.831408775981515</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>687.06697459584291</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>40.415704387990758</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:xVal>
+                <c:yVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Tabelle1!$J$69:$J$74</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="6"/>
+                      <c:pt idx="0">
+                        <c:v>0</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>130</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>0</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>20</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>170</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>10</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:yVal>
+                <c:smooth val="0"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000003-D15F-4363-97C5-9CF82FC49F12}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredScatterSeries>
+          </c:ext>
+        </c:extLst>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1026746751"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1500"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="5000"/>
+                  <a:lumOff val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="de-DE" b="1"/>
+                  <a:t>Height (µm)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="de-DE"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="in"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1026745311"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="250"/>
+        <c:minorUnit val="50"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1026745311"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="5000"/>
+                  <a:lumOff val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="de-DE" b="1"/>
+                  <a:t>Voltage (mV)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="2.8392900839877045E-2"/>
+              <c:y val="0.11797840554344781"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="de-DE"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1026746751"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="100"/>
+        <c:minorUnit val="20"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="de-DE"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.7" r="0.7" t="0.78740157499999996" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="de-DE"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="de-DE" b="1"/>
+              <a:t>Height of Unknown Profile</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="8.2783042540216401E-2"/>
+          <c:y val="0.11188377608235291"/>
+          <c:w val="0.70487116117557058"/>
+          <c:h val="0.52346535691270868"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Tabelle1!$K$68</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>assumed height</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:pattFill prst="ltUpDiag">
+              <a:fgClr>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:sysClr>
+              </a:fgClr>
+              <a:bgClr>
+                <a:schemeClr val="bg1"/>
+              </a:bgClr>
+            </a:pattFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>Tabelle1!$K$70:$K$74</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>700</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>50</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-C526-441D-B83E-34BC2EC3AF9D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="0"/>
+        <c:axId val="1826559727"/>
+        <c:axId val="1826557807"/>
+      </c:barChart>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Tabelle1!$H$68</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>slow scan</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>Tabelle1!$I$70:$I$74</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>525.40415704387988</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>80.831408775981515</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>687.06697459584291</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>40.415704387990758</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-C526-441D-B83E-34BC2EC3AF9D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Tabelle1!$Y$68</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>fast scan</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>Tabelle1!$Z$70:$Z$74</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>517.04545454545462</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>99.431818181818187</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>735.79545454545462</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>79.545454545454547</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-C526-441D-B83E-34BC2EC3AF9D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:axId val="1757685263"/>
+        <c:axId val="1757667503"/>
+      </c:barChart>
       <c:catAx>
-        <c:axId val="1034222495"/>
+        <c:axId val="1826559727"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="de-DE" b="1"/>
+                  <a:t>Measuring Point</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="de-DE"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1061,7 +4702,7 @@
             <a:endParaRPr lang="de-DE"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1034224895"/>
+        <c:crossAx val="1826557807"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1069,7 +4710,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1034224895"/>
+        <c:axId val="1826557807"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1089,6 +4730,91 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="5000"/>
+                  <a:lumOff val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="de-DE" b="1"/>
+                  <a:t>Height</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="de-DE" b="1" baseline="0"/>
+                  <a:t> </a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="de-DE" b="1"/>
+                  <a:t>(µm)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.13430354456348936"/>
+              <c:y val="4.420853767227579E-2"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="de-DE"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -1120,10 +4846,108 @@
             <a:endParaRPr lang="de-DE"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1034222495"/>
+        <c:crossAx val="1826559727"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
+        <c:minorUnit val="50"/>
       </c:valAx>
+      <c:valAx>
+        <c:axId val="1757667503"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="r"/>
+        <c:numFmt formatCode="0" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1757685263"/>
+        <c:crosses val="max"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:catAx>
+        <c:axId val="1757685263"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1757667503"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:dTable>
+        <c:showHorzBorder val="0"/>
+        <c:showVertBorder val="1"/>
+        <c:showOutline val="1"/>
+        <c:showKeys val="1"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr rtl="0">
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+      </c:dTable>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -1132,37 +4956,6 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="de-DE"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -1287,6 +5080,166 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
   <cs:axisTitle>
@@ -1791,6 +5744,2070 @@
 </file>
 
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -2549,23 +8566,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>461962</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>100012</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>486749</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>79849</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>461962</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>176212</xdr:rowOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>72993</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>79483</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="5" name="Diagramm 4">
+        <xdr:cNvPr id="6" name="Diagramm 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{30B57B97-D298-68CF-ECA0-B057EF908556}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C6318A19-C85B-270F-26C5-1E268CBD3222}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2578,6 +8595,158 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>623454</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>209698</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>190134</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="9" name="Diagramm 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B43FE8A0-A43C-4D37-B9AE-CB0FF3F66796}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>124443</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>35131</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>472687</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>34765</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="10" name="Diagramm 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{19B1ED45-B3A1-45CF-9B2A-D75AA97E43E3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>348244</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>190134</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="11" name="Diagramm 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DAB4515C-FBF9-4B20-A7EC-B7906B5FAAAF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>477849</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>104856</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>392204</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>179295</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="18" name="Diagramm 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E2F43A32-6E6F-4B82-BD61-8EC75BDB8126}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2903,7 +9072,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAC21238-07F0-4F79-A400-2B4B4E09B5E3}">
-  <dimension ref="A1:J67"/>
+  <dimension ref="A1:AK74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3030,12 +9199,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>3</v>
       </c>
@@ -3043,7 +9212,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>5</v>
       </c>
@@ -3051,17 +9220,17 @@
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>12</v>
       </c>
@@ -3071,8 +9240,22 @@
       <c r="E26" t="s">
         <v>66</v>
       </c>
+      <c r="I26">
+        <v>-68</v>
+      </c>
+      <c r="J26">
+        <v>-135</v>
+      </c>
+      <c r="L26">
+        <f>I26-I$26</f>
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <f>J26-J$26</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>13</v>
       </c>
@@ -3084,29 +9267,101 @@
         <f>1/(2*PI()*220000*100*10^-9)</f>
         <v>7.2343155950861515</v>
       </c>
+      <c r="I27">
+        <v>-46</v>
+      </c>
+      <c r="J27">
+        <v>-115</v>
+      </c>
+      <c r="L27">
+        <f t="shared" ref="L27:M31" si="0">I27-I$26</f>
+        <v>22</v>
+      </c>
+      <c r="M27">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>11</v>
       </c>
+      <c r="I28">
+        <v>-24</v>
+      </c>
+      <c r="J28">
+        <v>-95</v>
+      </c>
+      <c r="L28">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="M28">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="I29">
+        <v>-20</v>
+      </c>
+      <c r="J29">
+        <v>-85</v>
+      </c>
+      <c r="L29">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="M29">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>14</v>
       </c>
       <c r="B30" t="s">
         <v>17</v>
       </c>
+      <c r="I30">
+        <v>-6</v>
+      </c>
+      <c r="J30">
+        <v>-70</v>
+      </c>
+      <c r="L30">
+        <f t="shared" si="0"/>
+        <v>62</v>
+      </c>
+      <c r="M30">
+        <f t="shared" si="0"/>
+        <v>65</v>
+      </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>16</v>
       </c>
       <c r="B31" t="s">
         <v>15</v>
       </c>
+      <c r="I31">
+        <v>10</v>
+      </c>
+      <c r="J31">
+        <v>-55</v>
+      </c>
+      <c r="L31">
+        <f t="shared" si="0"/>
+        <v>78</v>
+      </c>
+      <c r="M31">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>20</v>
       </c>
@@ -3114,7 +9369,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>18</v>
       </c>
@@ -3122,7 +9377,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>22</v>
       </c>
@@ -3130,7 +9385,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>25</v>
       </c>
@@ -3138,15 +9393,89 @@
         <v>23</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="I38" t="s">
-        <v>30</v>
-      </c>
-      <c r="J38" t="s">
-        <v>32</v>
+    <row r="37" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="F37" t="s">
+        <v>71</v>
+      </c>
+      <c r="I37" t="s">
+        <v>73</v>
+      </c>
+      <c r="M37" t="s">
+        <v>74</v>
+      </c>
+      <c r="O37" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>75</v>
+      </c>
+      <c r="W37" t="s">
+        <v>71</v>
+      </c>
+      <c r="Z37" t="s">
+        <v>73</v>
+      </c>
+      <c r="AD37" t="s">
+        <v>74</v>
+      </c>
+      <c r="AF37" t="s">
+        <v>76</v>
+      </c>
+      <c r="AH37" t="s">
+        <v>75</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="F38">
+        <v>100</v>
+      </c>
+      <c r="G38">
+        <v>250</v>
+      </c>
+      <c r="H38" t="s">
+        <v>34</v>
+      </c>
+      <c r="I38">
+        <v>100</v>
+      </c>
+      <c r="J38">
+        <v>250</v>
+      </c>
+      <c r="K38" t="s">
+        <v>34</v>
+      </c>
+      <c r="M38">
+        <v>100</v>
+      </c>
+      <c r="N38">
+        <v>250</v>
+      </c>
+      <c r="W38">
+        <v>100</v>
+      </c>
+      <c r="X38">
+        <v>250</v>
+      </c>
+      <c r="Y38" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z38">
+        <v>100</v>
+      </c>
+      <c r="AA38">
+        <v>250</v>
+      </c>
+      <c r="AB38" t="s">
+        <v>34</v>
+      </c>
+      <c r="AD38">
+        <v>100</v>
+      </c>
+      <c r="AE38">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="39" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>28</v>
       </c>
@@ -3154,10 +9483,13 @@
         <v>0</v>
       </c>
       <c r="F39">
-        <v>-70</v>
+        <v>-72</v>
       </c>
       <c r="G39">
         <v>-275</v>
+      </c>
+      <c r="H39">
+        <v>-280</v>
       </c>
       <c r="I39">
         <f>F39-$F$39</f>
@@ -3167,8 +9499,36 @@
         <f>G39-$G$39</f>
         <v>0</v>
       </c>
+      <c r="K39">
+        <f>H39-$H$39</f>
+        <v>0</v>
+      </c>
+      <c r="V39">
+        <v>0</v>
+      </c>
+      <c r="W39">
+        <v>-140</v>
+      </c>
+      <c r="X39">
+        <v>-325</v>
+      </c>
+      <c r="Y39">
+        <v>-35</v>
+      </c>
+      <c r="Z39">
+        <f>W39-W$39</f>
+        <v>0</v>
+      </c>
+      <c r="AA39">
+        <f>X39-X$39</f>
+        <v>0</v>
+      </c>
+      <c r="AB39">
+        <f>Y39-Y$39</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>29</v>
       </c>
@@ -3184,16 +9544,91 @@
       <c r="G40">
         <v>-210</v>
       </c>
+      <c r="H40">
+        <v>-150</v>
+      </c>
       <c r="I40">
-        <f t="shared" ref="I40:J44" si="0">F40-$F$39</f>
-        <v>20</v>
+        <f t="shared" ref="I40:I44" si="1">F40-$F$39</f>
+        <v>22</v>
       </c>
       <c r="J40">
-        <f t="shared" ref="J40:J44" si="1">G40-$G$39</f>
+        <f t="shared" ref="J40:J44" si="2">G40-$G$39</f>
         <v>65</v>
       </c>
+      <c r="K40">
+        <f t="shared" ref="K40:K44" si="3">H40-$H$39</f>
+        <v>130</v>
+      </c>
+      <c r="M40">
+        <f>I40-I39</f>
+        <v>22</v>
+      </c>
+      <c r="N40">
+        <f>(J40-J39)/2.5</f>
+        <v>26</v>
+      </c>
+      <c r="O40">
+        <v>100</v>
+      </c>
+      <c r="P40">
+        <v>250</v>
+      </c>
+      <c r="Q40">
+        <f>O40*M40</f>
+        <v>2200</v>
+      </c>
+      <c r="R40">
+        <f>P40*N40</f>
+        <v>6500</v>
+      </c>
+      <c r="V40">
+        <v>1</v>
+      </c>
+      <c r="W40">
+        <v>-115</v>
+      </c>
+      <c r="X40">
+        <v>-270</v>
+      </c>
+      <c r="Y40">
+        <v>95</v>
+      </c>
+      <c r="Z40">
+        <f t="shared" ref="Z40:AB44" si="4">W40-W$39</f>
+        <v>25</v>
+      </c>
+      <c r="AA40">
+        <f t="shared" si="4"/>
+        <v>55</v>
+      </c>
+      <c r="AB40">
+        <f t="shared" si="4"/>
+        <v>130</v>
+      </c>
+      <c r="AD40">
+        <f>Z40-Z39</f>
+        <v>25</v>
+      </c>
+      <c r="AE40">
+        <f>(AA40-AA39)/2.5</f>
+        <v>22</v>
+      </c>
+      <c r="AF40">
+        <v>100</v>
+      </c>
+      <c r="AG40">
+        <v>250</v>
+      </c>
+      <c r="AH40">
+        <f>AF40*AD40</f>
+        <v>2500</v>
+      </c>
+      <c r="AI40">
+        <f>AG40*AE40</f>
+        <v>5500</v>
+      </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>31</v>
       </c>
@@ -3204,21 +9639,96 @@
         <v>2</v>
       </c>
       <c r="F41">
+        <v>-36</v>
+      </c>
+      <c r="G41">
+        <v>-140</v>
+      </c>
+      <c r="H41">
+        <v>-280</v>
+      </c>
+      <c r="I41">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="J41">
+        <f t="shared" si="2"/>
+        <v>135</v>
+      </c>
+      <c r="K41">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M41">
+        <f t="shared" ref="M41:M44" si="5">I41-I40</f>
+        <v>14</v>
+      </c>
+      <c r="N41">
+        <f t="shared" ref="N41:N44" si="6">(J41-J40)/2.5</f>
+        <v>28</v>
+      </c>
+      <c r="O41">
+        <v>100</v>
+      </c>
+      <c r="P41">
+        <v>250</v>
+      </c>
+      <c r="Q41">
+        <f>O41*M41</f>
+        <v>1400</v>
+      </c>
+      <c r="R41">
+        <f>P41*N41</f>
+        <v>7000</v>
+      </c>
+      <c r="V41">
+        <v>2</v>
+      </c>
+      <c r="W41">
+        <v>-105</v>
+      </c>
+      <c r="X41">
+        <v>-190</v>
+      </c>
+      <c r="Y41">
         <v>-35</v>
       </c>
-      <c r="G41">
-        <v>-125</v>
-      </c>
-      <c r="I41">
-        <f t="shared" si="0"/>
+      <c r="Z41">
+        <f t="shared" si="4"/>
         <v>35</v>
       </c>
-      <c r="J41">
-        <f t="shared" si="1"/>
-        <v>150</v>
+      <c r="AA41">
+        <f t="shared" si="4"/>
+        <v>135</v>
+      </c>
+      <c r="AB41">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AD41">
+        <f>Z41-Z40</f>
+        <v>10</v>
+      </c>
+      <c r="AE41">
+        <f>(AA41-AA40)/2.5</f>
+        <v>32</v>
+      </c>
+      <c r="AF41">
+        <v>100</v>
+      </c>
+      <c r="AG41">
+        <v>250</v>
+      </c>
+      <c r="AH41">
+        <f>AF41*AD41</f>
+        <v>1000</v>
+      </c>
+      <c r="AI41">
+        <f>AG41*AE41</f>
+        <v>8000</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>33</v>
       </c>
@@ -3229,40 +9739,190 @@
         <v>3</v>
       </c>
       <c r="F42">
-        <v>-30</v>
+        <v>-32</v>
       </c>
       <c r="G42">
-        <v>-55</v>
+        <v>-60</v>
+      </c>
+      <c r="H42">
+        <v>-260</v>
       </c>
       <c r="I42">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>40</v>
       </c>
       <c r="J42">
-        <f t="shared" si="1"/>
-        <v>220</v>
+        <f t="shared" si="2"/>
+        <v>215</v>
+      </c>
+      <c r="K42">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="M42">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="N42">
+        <f t="shared" si="6"/>
+        <v>32</v>
+      </c>
+      <c r="O42">
+        <v>100</v>
+      </c>
+      <c r="P42">
+        <v>250</v>
+      </c>
+      <c r="Q42">
+        <f>O42*M42</f>
+        <v>400</v>
+      </c>
+      <c r="R42">
+        <f>P42*N42</f>
+        <v>8000</v>
+      </c>
+      <c r="V42">
+        <v>3</v>
+      </c>
+      <c r="W42">
+        <v>-95</v>
+      </c>
+      <c r="X42">
+        <v>-110</v>
+      </c>
+      <c r="Y42">
+        <v>-10</v>
+      </c>
+      <c r="Z42">
+        <f t="shared" si="4"/>
+        <v>45</v>
+      </c>
+      <c r="AA42">
+        <f t="shared" si="4"/>
+        <v>215</v>
+      </c>
+      <c r="AB42">
+        <f t="shared" si="4"/>
+        <v>25</v>
+      </c>
+      <c r="AD42">
+        <f>Z42-Z41</f>
+        <v>10</v>
+      </c>
+      <c r="AE42">
+        <f>(AA42-AA41)/2.5</f>
+        <v>32</v>
+      </c>
+      <c r="AF42">
+        <v>100</v>
+      </c>
+      <c r="AG42">
+        <v>250</v>
+      </c>
+      <c r="AH42">
+        <f>AF42*AD42</f>
+        <v>1000</v>
+      </c>
+      <c r="AI42">
+        <f>AG42*AE42</f>
+        <v>8000</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:37" x14ac:dyDescent="0.25">
       <c r="E43">
         <v>4</v>
       </c>
       <c r="F43">
-        <v>-15</v>
+        <v>-18</v>
       </c>
       <c r="G43">
-        <v>20</v>
+        <v>10</v>
+      </c>
+      <c r="H43">
+        <v>-110</v>
       </c>
       <c r="I43">
-        <f t="shared" si="0"/>
-        <v>55</v>
+        <f t="shared" si="1"/>
+        <v>54</v>
       </c>
       <c r="J43">
-        <f t="shared" si="1"/>
-        <v>295</v>
+        <f t="shared" si="2"/>
+        <v>285</v>
+      </c>
+      <c r="K43">
+        <f t="shared" si="3"/>
+        <v>170</v>
+      </c>
+      <c r="M43">
+        <f t="shared" si="5"/>
+        <v>14</v>
+      </c>
+      <c r="N43">
+        <f t="shared" si="6"/>
+        <v>28</v>
+      </c>
+      <c r="O43">
+        <v>100</v>
+      </c>
+      <c r="P43">
+        <v>250</v>
+      </c>
+      <c r="Q43">
+        <f>O43*M43</f>
+        <v>1400</v>
+      </c>
+      <c r="R43">
+        <f>P43*N43</f>
+        <v>7000</v>
+      </c>
+      <c r="V43">
+        <v>4</v>
+      </c>
+      <c r="W43">
+        <v>-80</v>
+      </c>
+      <c r="X43">
+        <v>-40</v>
+      </c>
+      <c r="Y43">
+        <v>150</v>
+      </c>
+      <c r="Z43">
+        <f t="shared" si="4"/>
+        <v>60</v>
+      </c>
+      <c r="AA43">
+        <f t="shared" si="4"/>
+        <v>285</v>
+      </c>
+      <c r="AB43">
+        <f t="shared" si="4"/>
+        <v>185</v>
+      </c>
+      <c r="AD43">
+        <f>Z43-Z42</f>
+        <v>15</v>
+      </c>
+      <c r="AE43">
+        <f>(AA43-AA42)/2.5</f>
+        <v>28</v>
+      </c>
+      <c r="AF43">
+        <v>100</v>
+      </c>
+      <c r="AG43">
+        <v>250</v>
+      </c>
+      <c r="AH43">
+        <f>AF43*AD43</f>
+        <v>1500</v>
+      </c>
+      <c r="AI43">
+        <f>AG43*AE43</f>
+        <v>7000</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>35</v>
       </c>
@@ -3270,21 +9930,96 @@
         <v>5</v>
       </c>
       <c r="F44">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G44">
-        <v>95</v>
+        <v>80</v>
+      </c>
+      <c r="H44">
+        <v>-270</v>
       </c>
       <c r="I44">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>78</v>
       </c>
       <c r="J44">
-        <f t="shared" si="1"/>
-        <v>370</v>
+        <f t="shared" si="2"/>
+        <v>355</v>
+      </c>
+      <c r="K44">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="M44">
+        <f t="shared" si="5"/>
+        <v>24</v>
+      </c>
+      <c r="N44">
+        <f t="shared" si="6"/>
+        <v>28</v>
+      </c>
+      <c r="O44">
+        <v>100</v>
+      </c>
+      <c r="P44">
+        <v>250</v>
+      </c>
+      <c r="Q44">
+        <f>O44*M44</f>
+        <v>2400</v>
+      </c>
+      <c r="R44">
+        <f>P44*N44</f>
+        <v>7000</v>
+      </c>
+      <c r="V44">
+        <v>5</v>
+      </c>
+      <c r="W44">
+        <v>-65</v>
+      </c>
+      <c r="X44">
+        <v>40</v>
+      </c>
+      <c r="Y44">
+        <v>-15</v>
+      </c>
+      <c r="Z44">
+        <f t="shared" si="4"/>
+        <v>75</v>
+      </c>
+      <c r="AA44">
+        <f t="shared" si="4"/>
+        <v>365</v>
+      </c>
+      <c r="AB44">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="AD44">
+        <f>Z44-Z43</f>
+        <v>15</v>
+      </c>
+      <c r="AE44">
+        <f>(AA44-AA43)/2.5</f>
+        <v>32</v>
+      </c>
+      <c r="AF44">
+        <v>100</v>
+      </c>
+      <c r="AG44">
+        <v>250</v>
+      </c>
+      <c r="AH44">
+        <f>AF44*AD44</f>
+        <v>1500</v>
+      </c>
+      <c r="AI44">
+        <f>AG44*AE44</f>
+        <v>8000</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>36</v>
       </c>
@@ -3300,10 +10035,50 @@
       </c>
       <c r="G45">
         <f>(G44-G39)/5</f>
-        <v>74</v>
+        <v>71</v>
+      </c>
+      <c r="H45">
+        <f>(H44-H39)/5</f>
+        <v>2</v>
+      </c>
+      <c r="L45" t="s">
+        <v>72</v>
+      </c>
+      <c r="M45">
+        <f>AVERAGE(M40:M44)</f>
+        <v>15.6</v>
+      </c>
+      <c r="N45">
+        <f>AVERAGE(N40:N44)</f>
+        <v>28.4</v>
+      </c>
+      <c r="S45" t="s">
+        <v>77</v>
+      </c>
+      <c r="T45">
+        <f>SUM(Q40:R44)/SUM(O40:P44)</f>
+        <v>24.742857142857144</v>
+      </c>
+      <c r="AC45" t="s">
+        <v>72</v>
+      </c>
+      <c r="AD45">
+        <f>AVERAGE(AD40:AD44)</f>
+        <v>15</v>
+      </c>
+      <c r="AE45">
+        <f>AVERAGE(AE40:AE44)</f>
+        <v>29.2</v>
+      </c>
+      <c r="AJ45" t="s">
+        <v>77</v>
+      </c>
+      <c r="AK45">
+        <f>SUM(AH40:AI44)/SUM(AF40:AG44)</f>
+        <v>25.142857142857142</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>38</v>
       </c>
@@ -3311,46 +10086,156 @@
         <v>39</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>40</v>
       </c>
       <c r="B47" t="s">
         <v>41</v>
       </c>
+      <c r="Z47" t="s">
+        <v>68</v>
+      </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="I48" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+      <c r="AA48">
+        <f>Z39</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="Z49">
+        <v>100</v>
+      </c>
+      <c r="AA49">
+        <f t="shared" ref="AA49:AA53" si="7">Z40</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="50" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>42</v>
       </c>
+      <c r="I50">
+        <v>100</v>
+      </c>
+      <c r="J50">
+        <f>I40</f>
+        <v>22</v>
+      </c>
+      <c r="Z50">
+        <v>200</v>
+      </c>
+      <c r="AA50">
+        <f t="shared" si="7"/>
+        <v>35</v>
+      </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>43</v>
       </c>
+      <c r="I51">
+        <v>200</v>
+      </c>
+      <c r="J51">
+        <f>I41</f>
+        <v>36</v>
+      </c>
+      <c r="Z51">
+        <v>300</v>
+      </c>
+      <c r="AA51">
+        <f t="shared" si="7"/>
+        <v>45</v>
+      </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="I52">
+        <v>300</v>
+      </c>
+      <c r="J52">
+        <f>I42</f>
+        <v>40</v>
+      </c>
+      <c r="Z52">
+        <v>400</v>
+      </c>
+      <c r="AA52">
+        <f t="shared" si="7"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="53" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>44</v>
       </c>
+      <c r="I53">
+        <v>400</v>
+      </c>
+      <c r="J53">
+        <f>I43</f>
+        <v>54</v>
+      </c>
+      <c r="Z53">
+        <v>500</v>
+      </c>
+      <c r="AA53">
+        <f t="shared" si="7"/>
+        <v>75</v>
+      </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>45</v>
       </c>
       <c r="B54" t="s">
         <v>46</v>
       </c>
+      <c r="I54">
+        <v>500</v>
+      </c>
+      <c r="J54">
+        <f>I44</f>
+        <v>78</v>
+      </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="Z55" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="56" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>47</v>
       </c>
       <c r="B56" t="s">
         <v>4</v>
       </c>
+      <c r="I56" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+      <c r="AA56">
+        <f>AA39</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>48</v>
       </c>
@@ -3363,8 +10248,21 @@
       <c r="D57" s="2" t="s">
         <v>53</v>
       </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>0</v>
+      </c>
+      <c r="Z57">
+        <v>250</v>
+      </c>
+      <c r="AA57">
+        <f t="shared" ref="AA57:AA61" si="8">AA40</f>
+        <v>55</v>
+      </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>49</v>
       </c>
@@ -3377,13 +10275,57 @@
       <c r="D58" s="1" t="s">
         <v>52</v>
       </c>
+      <c r="I58">
+        <v>250</v>
+      </c>
+      <c r="J58">
+        <f>J40</f>
+        <v>65</v>
+      </c>
+      <c r="Z58">
+        <v>500</v>
+      </c>
+      <c r="AA58">
+        <f t="shared" si="8"/>
+        <v>135</v>
+      </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="I59">
+        <v>500</v>
+      </c>
+      <c r="J59">
+        <f>J41</f>
+        <v>135</v>
+      </c>
+      <c r="Z59">
+        <v>750</v>
+      </c>
+      <c r="AA59">
+        <f t="shared" si="8"/>
+        <v>215</v>
+      </c>
+    </row>
+    <row r="60" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>54</v>
       </c>
+      <c r="I60">
+        <v>750</v>
+      </c>
+      <c r="J60">
+        <f>J42</f>
+        <v>215</v>
+      </c>
+      <c r="Z60">
+        <v>1000</v>
+      </c>
+      <c r="AA60">
+        <f t="shared" si="8"/>
+        <v>285</v>
+      </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>55</v>
       </c>
@@ -3396,42 +10338,298 @@
       <c r="D61" t="s">
         <v>59</v>
       </c>
+      <c r="I61">
+        <v>1000</v>
+      </c>
+      <c r="J61">
+        <f>J43</f>
+        <v>285</v>
+      </c>
+      <c r="Z61">
+        <v>1250</v>
+      </c>
+      <c r="AA61">
+        <f t="shared" si="8"/>
+        <v>365</v>
+      </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>56</v>
       </c>
       <c r="B62" t="s">
         <v>57</v>
       </c>
+      <c r="I62">
+        <v>1250</v>
+      </c>
+      <c r="J62">
+        <f>J44</f>
+        <v>355</v>
+      </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>60</v>
       </c>
+      <c r="I64" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z64" t="s">
+        <v>70</v>
+      </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>62</v>
       </c>
       <c r="B65">
         <v>250</v>
       </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>0</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+      <c r="AA65">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>63</v>
       </c>
       <c r="B66">
         <v>100</v>
       </c>
+      <c r="I66">
+        <v>1500</v>
+      </c>
+      <c r="J66">
+        <f>I66*T45/100</f>
+        <v>371.14285714285717</v>
+      </c>
+      <c r="Z66">
+        <v>1500</v>
+      </c>
+      <c r="AA66">
+        <f>Z66*AK45/100</f>
+        <v>377.14285714285711</v>
+      </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>64</v>
       </c>
       <c r="B67" t="s">
         <v>34</v>
+      </c>
+    </row>
+    <row r="68" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="H68" t="s">
+        <v>78</v>
+      </c>
+      <c r="I68" t="s">
+        <v>34</v>
+      </c>
+      <c r="K68" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y68" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z68" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="69" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="I69">
+        <f>J69/$T$45*100</f>
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <f>K39</f>
+        <v>0</v>
+      </c>
+      <c r="L69" t="e">
+        <f>K69/I69</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z69">
+        <f>AA69/$AK$45*100</f>
+        <v>0</v>
+      </c>
+      <c r="AA69">
+        <f>AB39</f>
+        <v>0</v>
+      </c>
+      <c r="AC69" t="e">
+        <f>AB69/Z69</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="70" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="I70" s="3">
+        <f t="shared" ref="I70:I74" si="9">J70/$T$45*100</f>
+        <v>525.40415704387988</v>
+      </c>
+      <c r="J70">
+        <f>K40</f>
+        <v>130</v>
+      </c>
+      <c r="K70">
+        <v>500</v>
+      </c>
+      <c r="L70">
+        <f>K70/I70</f>
+        <v>0.95164835164835171</v>
+      </c>
+      <c r="Z70" s="3">
+        <f t="shared" ref="Z70:Z74" si="10">AA70/$AK$45*100</f>
+        <v>517.04545454545462</v>
+      </c>
+      <c r="AA70">
+        <f>AB40</f>
+        <v>130</v>
+      </c>
+      <c r="AB70">
+        <v>500</v>
+      </c>
+      <c r="AC70">
+        <f>AB70/Z70</f>
+        <v>0.96703296703296693</v>
+      </c>
+    </row>
+    <row r="71" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="I71" s="3">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <f>K41</f>
+        <v>0</v>
+      </c>
+      <c r="K71">
+        <v>0</v>
+      </c>
+      <c r="L71" t="e">
+        <f>K71/I71</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z71" s="3">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AA71">
+        <f>AB41</f>
+        <v>0</v>
+      </c>
+      <c r="AB71">
+        <v>0</v>
+      </c>
+      <c r="AC71" t="e">
+        <f>AB71/Z71</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="72" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="I72" s="3">
+        <f t="shared" si="9"/>
+        <v>80.831408775981515</v>
+      </c>
+      <c r="J72">
+        <f>K42</f>
+        <v>20</v>
+      </c>
+      <c r="K72">
+        <v>100</v>
+      </c>
+      <c r="L72">
+        <f>K72/I72</f>
+        <v>1.2371428571428573</v>
+      </c>
+      <c r="Z72" s="3">
+        <f t="shared" si="10"/>
+        <v>99.431818181818187</v>
+      </c>
+      <c r="AA72">
+        <f>AB42</f>
+        <v>25</v>
+      </c>
+      <c r="AB72">
+        <v>100</v>
+      </c>
+      <c r="AC72">
+        <f>AB72/Z72</f>
+        <v>1.0057142857142856</v>
+      </c>
+    </row>
+    <row r="73" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="I73" s="3">
+        <f t="shared" si="9"/>
+        <v>687.06697459584291</v>
+      </c>
+      <c r="J73">
+        <f>K43</f>
+        <v>170</v>
+      </c>
+      <c r="K73">
+        <v>700</v>
+      </c>
+      <c r="L73">
+        <f>K73/I73</f>
+        <v>1.0188235294117647</v>
+      </c>
+      <c r="Z73" s="3">
+        <f t="shared" si="10"/>
+        <v>735.79545454545462</v>
+      </c>
+      <c r="AA73">
+        <f>AB43</f>
+        <v>185</v>
+      </c>
+      <c r="AB73">
+        <v>700</v>
+      </c>
+      <c r="AC73">
+        <f>AB73/Z73</f>
+        <v>0.95135135135135129</v>
+      </c>
+    </row>
+    <row r="74" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="I74" s="3">
+        <f t="shared" si="9"/>
+        <v>40.415704387990758</v>
+      </c>
+      <c r="J74">
+        <f>K44</f>
+        <v>10</v>
+      </c>
+      <c r="K74">
+        <v>50</v>
+      </c>
+      <c r="L74">
+        <f>K74/I74</f>
+        <v>1.2371428571428573</v>
+      </c>
+      <c r="Z74" s="3">
+        <f t="shared" si="10"/>
+        <v>79.545454545454547</v>
+      </c>
+      <c r="AA74">
+        <f>AB44</f>
+        <v>20</v>
+      </c>
+      <c r="AB74">
+        <v>50</v>
+      </c>
+      <c r="AC74">
+        <f>AB74/Z74</f>
+        <v>0.62857142857142856</v>
       </c>
     </row>
   </sheetData>

--- a/AFM/MechsysLU_AFM.xlsx
+++ b/AFM/MechsysLU_AFM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\7_TU\Master Automatisierung und Robotische Systeme\Mechatronische Systeme Labor\AFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9B8A663-E698-4C10-8509-8BB15CA6B18B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{241A762F-BFAB-4D7C-91FD-83C6940825D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B84AB7BC-A147-41D7-A40F-EB74A04C0736}"/>
+    <workbookView xWindow="0" yWindow="300" windowWidth="29040" windowHeight="15840" xr2:uid="{B84AB7BC-A147-41D7-A40F-EB74A04C0736}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="89">
   <si>
     <t>V</t>
   </si>
@@ -280,11 +280,38 @@
   <si>
     <t>assumed height</t>
   </si>
+  <si>
+    <t>pos</t>
+  </si>
+  <si>
+    <t>stddev</t>
+  </si>
+  <si>
+    <t>stddev (fast+slow)</t>
+  </si>
+  <si>
+    <t>stddev pc</t>
+  </si>
+  <si>
+    <t>tapping mode</t>
+  </si>
+  <si>
+    <t>contact mode</t>
+  </si>
+  <si>
+    <t>contact mode (slow)</t>
+  </si>
+  <si>
+    <t>contact mode (fast)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="171" formatCode="0.0"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -314,11 +341,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -716,7 +744,7 @@
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
@@ -756,7 +784,7 @@
             <a:effectLst/>
           </c:spPr>
           <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr>
@@ -1060,7 +1088,7 @@
             <c:numRef>
               <c:f>Tabelle1!$J$49:$J$54</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
@@ -1159,7 +1187,7 @@
             <c:numRef>
               <c:f>Tabelle1!$J$57:$J$62</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
@@ -1295,9 +1323,9 @@
             <c:numRef>
               <c:f>Tabelle1!$I$69:$I$74</c:f>
               <c:numCache>
-                <c:formatCode>0</c:formatCode>
+                <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="6"/>
-                <c:pt idx="0" formatCode="General">
+                <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
@@ -1322,7 +1350,7 @@
             <c:numRef>
               <c:f>Tabelle1!$J$69:$J$74</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
@@ -1536,7 +1564,7 @@
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
@@ -1576,7 +1604,7 @@
             <a:effectLst/>
           </c:spPr>
           <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr>
@@ -1596,7 +1624,7 @@
             </a:p>
           </c:txPr>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1888,7 +1916,7 @@
             <c:numRef>
               <c:f>Tabelle1!$J$49:$J$54</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
@@ -1987,7 +2015,7 @@
             <c:numRef>
               <c:f>Tabelle1!$J$57:$J$62</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
@@ -2119,7 +2147,7 @@
                 <c:order val="3"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Tabelle1!$I$68</c15:sqref>
@@ -2160,7 +2188,7 @@
                 </c:marker>
                 <c:xVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Tabelle1!$I$69:$I$74</c15:sqref>
@@ -2168,9 +2196,9 @@
                       </c:ext>
                     </c:extLst>
                     <c:numCache>
-                      <c:formatCode>0</c:formatCode>
+                      <c:formatCode>0.0</c:formatCode>
                       <c:ptCount val="6"/>
-                      <c:pt idx="0" formatCode="General">
+                      <c:pt idx="0">
                         <c:v>0</c:v>
                       </c:pt>
                       <c:pt idx="1">
@@ -2193,7 +2221,7 @@
                 </c:xVal>
                 <c:yVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Tabelle1!$J$69:$J$74</c15:sqref>
@@ -2201,7 +2229,7 @@
                       </c:ext>
                     </c:extLst>
                     <c:numCache>
-                      <c:formatCode>General</c:formatCode>
+                      <c:formatCode>0.0</c:formatCode>
                       <c:ptCount val="6"/>
                       <c:pt idx="0">
                         <c:v>0</c:v>
@@ -2225,7 +2253,7 @@
                   </c:numRef>
                 </c:yVal>
                 <c:smooth val="0"/>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000003-A360-44EE-9FC4-09E762D509E9}"/>
                   </c:ext>
@@ -2408,7 +2436,7 @@
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
@@ -2448,7 +2476,7 @@
             <a:effectLst/>
           </c:spPr>
           <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr>
@@ -2468,7 +2496,7 @@
             </a:p>
           </c:txPr>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2995,9 +3023,9 @@
             <c:numRef>
               <c:f>Tabelle1!$I$69:$I$74</c:f>
               <c:numCache>
-                <c:formatCode>0</c:formatCode>
+                <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="6"/>
-                <c:pt idx="0" formatCode="General">
+                <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
@@ -3022,7 +3050,7 @@
             <c:numRef>
               <c:f>Tabelle1!$J$69:$J$74</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
@@ -3236,7 +3264,7 @@
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
@@ -3276,7 +3304,7 @@
             <a:effectLst/>
           </c:spPr>
           <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr>
@@ -3831,7 +3859,7 @@
                 <c:order val="3"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Tabelle1!$I$68</c15:sqref>
@@ -3872,7 +3900,7 @@
                 </c:marker>
                 <c:xVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Tabelle1!$I$69:$I$74</c15:sqref>
@@ -3880,9 +3908,9 @@
                       </c:ext>
                     </c:extLst>
                     <c:numCache>
-                      <c:formatCode>0</c:formatCode>
+                      <c:formatCode>0.0</c:formatCode>
                       <c:ptCount val="6"/>
-                      <c:pt idx="0" formatCode="General">
+                      <c:pt idx="0">
                         <c:v>0</c:v>
                       </c:pt>
                       <c:pt idx="1">
@@ -3905,7 +3933,7 @@
                 </c:xVal>
                 <c:yVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Tabelle1!$J$69:$J$74</c15:sqref>
@@ -3913,7 +3941,7 @@
                       </c:ext>
                     </c:extLst>
                     <c:numCache>
-                      <c:formatCode>General</c:formatCode>
+                      <c:formatCode>0.0</c:formatCode>
                       <c:ptCount val="6"/>
                       <c:pt idx="0">
                         <c:v>0</c:v>
@@ -3937,7 +3965,7 @@
                   </c:numRef>
                 </c:yVal>
                 <c:smooth val="0"/>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000003-D15F-4363-97C5-9CF82FC49F12}"/>
                   </c:ext>
@@ -4120,7 +4148,7 @@
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
@@ -4160,7 +4188,7 @@
             <a:effectLst/>
           </c:spPr>
           <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr>
@@ -4428,7 +4456,7 @@
             <c:numRef>
               <c:f>Tabelle1!$K$70:$K$74</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>500</c:v>
@@ -4437,7 +4465,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>100</c:v>
+                  <c:v>75</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>700</c:v>
@@ -4498,7 +4526,7 @@
             <c:numRef>
               <c:f>Tabelle1!$I$70:$I$74</c:f>
               <c:numCache>
-                <c:formatCode>0</c:formatCode>
+                <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>525.40415704387988</c:v>
@@ -4552,7 +4580,7 @@
             <c:numRef>
               <c:f>Tabelle1!$Z$70:$Z$74</c:f>
               <c:numCache>
-                <c:formatCode>0</c:formatCode>
+                <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>517.04545454545462</c:v>
@@ -4815,7 +4843,7 @@
             </a:p>
           </c:txPr>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -4858,7 +4886,7 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="r"/>
-        <c:numFmt formatCode="0" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -4904,6 +4932,1584 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="1757667503"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:dTable>
+        <c:showHorzBorder val="0"/>
+        <c:showVertBorder val="1"/>
+        <c:showOutline val="1"/>
+        <c:showKeys val="1"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr rtl="0">
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+      </c:dTable>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="de-DE"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.7" r="0.7" t="0.78740157499999996" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="de-DE"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="de-DE" b="1"/>
+              <a:t>AFM</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="de-DE" b="1" baseline="0"/>
+              <a:t> Readout Voltage and Height</a:t>
+            </a:r>
+            <a:br>
+              <a:rPr lang="de-DE" b="1" baseline="0"/>
+            </a:br>
+            <a:r>
+              <a:rPr lang="de-DE" b="1" baseline="0"/>
+              <a:t>(tapping mode)</a:t>
+            </a:r>
+            <a:endParaRPr lang="de-DE" b="1"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="9.1358477343806532E-2"/>
+          <c:y val="0.225777111031049"/>
+          <c:w val="0.67090229671536605"/>
+          <c:h val="0.58952026391620516"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Tabelle1!$I$126</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>100 µm</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Tabelle1!$I$127:$I$132</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>500</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Tabelle1!$J$127:$J$132</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>80</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-89BA-487B-B362-AB269DAB26AB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Tabelle1!$I$134</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>250 µm</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Tabelle1!$I$135:$I$140</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>750</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1250</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Tabelle1!$J$135:$J$140</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>240</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>320</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>390</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-89BA-487B-B362-AB269DAB26AB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Tabelle1!$I$142</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Average</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="12700" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Tabelle1!$I$143:$I$144</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1500</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Tabelle1!$J$143:$J$144</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>402.85714285714289</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-89BA-487B-B362-AB269DAB26AB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Tabelle1!$I$146</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>???</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Tabelle1!$I$147:$I$152</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>502.65957446808505</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>55.851063829787229</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>670.21276595744678</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>37.234042553191486</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Tabelle1!$J$147:$J$152</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>135</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-89BA-487B-B362-AB269DAB26AB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1026746751"/>
+        <c:axId val="1026745311"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1026746751"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1500"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="5000"/>
+                  <a:lumOff val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="de-DE" b="1"/>
+                  <a:t>Height (µm)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="de-DE"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="in"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1026745311"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="250"/>
+        <c:minorUnit val="50"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1026745311"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="5000"/>
+                  <a:lumOff val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="de-DE" b="1"/>
+                  <a:t>Voltage (mV)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="3.0974073643502232E-2"/>
+              <c:y val="0.12214557259828444"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="de-DE"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1026746751"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="100"/>
+        <c:minorUnit val="20"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="de-DE"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.7" r="0.7" t="0.78740157499999996" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="de-DE"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="de-DE" b="1"/>
+              <a:t>Height of Unknown Profile</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="8.2783042540216401E-2"/>
+          <c:y val="0.12086011421686318"/>
+          <c:w val="0.70487116117557058"/>
+          <c:h val="0.404681349092887"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Tabelle1!$K$146</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>assumed height</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:pattFill prst="ltUpDiag">
+              <a:fgClr>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:sysClr>
+              </a:fgClr>
+              <a:bgClr>
+                <a:schemeClr val="bg1"/>
+              </a:bgClr>
+            </a:pattFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>Tabelle1!$K$148:$K$152</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>700</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>50</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-20FF-493B-BE38-68F7BC1E90D5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="0"/>
+        <c:axId val="1826559727"/>
+        <c:axId val="1826557807"/>
+      </c:barChart>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Tabelle1!$H$146</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>tapping mode</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent6"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>Tabelle1!$I$148:$I$152</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>502.65957446808505</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>55.851063829787229</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>670.21276595744678</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>37.234042553191486</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-20FF-493B-BE38-68F7BC1E90D5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Tabelle1!$P$146</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>contact mode (slow)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>Tabelle1!$P$148:$P$152</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>525.40415704387988</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>80.831408775981515</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>687.06697459584291</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>40.415704387990758</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-20FF-493B-BE38-68F7BC1E90D5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Tabelle1!$Q$146</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>contact mode (fast)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>Tabelle1!$Q$148:$Q$152</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>517.04545454545462</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>99.431818181818187</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>735.79545454545462</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>79.545454545454547</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-20FF-493B-BE38-68F7BC1E90D5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:axId val="1757685263"/>
+        <c:axId val="1757667503"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1826559727"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="de-DE" b="1"/>
+                  <a:t>Measuring Point</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="de-DE"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1826557807"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1826557807"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="5000"/>
+                  <a:lumOff val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="de-DE" b="1"/>
+                  <a:t>Height</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="de-DE" b="1" baseline="0"/>
+                  <a:t> </a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="de-DE" b="1"/>
+                  <a:t>(µm)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.13430354456348936"/>
+              <c:y val="4.420853767227579E-2"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="de-DE"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1826559727"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:minorUnit val="50"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1757667503"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="r"/>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1757685263"/>
+        <c:crosses val="max"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:catAx>
+        <c:axId val="1757685263"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1757667503"/>
+        <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
@@ -5240,6 +6846,86 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
   <cs:axisTitle>
@@ -7808,6 +9494,1038 @@
 </file>
 
 <file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -8334,7 +11052,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>472440</xdr:colOff>
+      <xdr:colOff>91440</xdr:colOff>
       <xdr:row>15</xdr:row>
       <xdr:rowOff>127635</xdr:rowOff>
     </xdr:to>
@@ -8374,8 +11092,8 @@
       <xdr:row>9</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="3" name="Rechteck 2">
@@ -8498,7 +11216,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="3" name="Rechteck 2">
@@ -8717,15 +11435,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>21</xdr:col>
-      <xdr:colOff>477849</xdr:colOff>
-      <xdr:row>82</xdr:row>
-      <xdr:rowOff>104856</xdr:rowOff>
+      <xdr:colOff>612320</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>48827</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>28</xdr:col>
-      <xdr:colOff>392204</xdr:colOff>
-      <xdr:row>107</xdr:row>
-      <xdr:rowOff>179295</xdr:rowOff>
+      <xdr:colOff>526675</xdr:colOff>
+      <xdr:row>102</xdr:row>
+      <xdr:rowOff>123266</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -8747,6 +11465,82 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>481854</xdr:colOff>
+      <xdr:row>126</xdr:row>
+      <xdr:rowOff>134471</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>68098</xdr:colOff>
+      <xdr:row>142</xdr:row>
+      <xdr:rowOff>134105</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Diagramm 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED806DEB-2567-4133-BDB2-51D2AA06FA0B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>156881</xdr:colOff>
+      <xdr:row>115</xdr:row>
+      <xdr:rowOff>22412</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>71236</xdr:colOff>
+      <xdr:row>140</xdr:row>
+      <xdr:rowOff>96851</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Diagramm 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC6881A6-4CFE-4361-8C11-7AA1A0E16177}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -9072,8 +11866,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAC21238-07F0-4F79-A400-2B4B4E09B5E3}">
-  <dimension ref="A1:AK74"/>
+  <dimension ref="A1:AK152"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="9" max="9" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -9384,6 +12182,15 @@
       <c r="B34" t="s">
         <v>24</v>
       </c>
+      <c r="E34" t="s">
+        <v>81</v>
+      </c>
+      <c r="F34">
+        <v>-21.25</v>
+      </c>
+      <c r="G34">
+        <v>256.25</v>
+      </c>
     </row>
     <row r="35" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
@@ -9574,11 +12381,11 @@
         <v>250</v>
       </c>
       <c r="Q40">
-        <f>O40*M40</f>
+        <f t="shared" ref="Q40:R44" si="4">O40*M40</f>
         <v>2200</v>
       </c>
       <c r="R40">
-        <f>P40*N40</f>
+        <f t="shared" si="4"/>
         <v>6500</v>
       </c>
       <c r="V40">
@@ -9594,15 +12401,15 @@
         <v>95</v>
       </c>
       <c r="Z40">
-        <f t="shared" ref="Z40:AB44" si="4">W40-W$39</f>
+        <f t="shared" ref="Z40:AB44" si="5">W40-W$39</f>
         <v>25</v>
       </c>
       <c r="AA40">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>55</v>
       </c>
       <c r="AB40">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>130</v>
       </c>
       <c r="AD40">
@@ -9620,11 +12427,11 @@
         <v>250</v>
       </c>
       <c r="AH40">
-        <f>AF40*AD40</f>
+        <f t="shared" ref="AH40:AI44" si="6">AF40*AD40</f>
         <v>2500</v>
       </c>
       <c r="AI40">
-        <f>AG40*AE40</f>
+        <f t="shared" si="6"/>
         <v>5500</v>
       </c>
     </row>
@@ -9660,11 +12467,11 @@
         <v>0</v>
       </c>
       <c r="M41">
-        <f t="shared" ref="M41:M44" si="5">I41-I40</f>
+        <f t="shared" ref="M41:M44" si="7">I41-I40</f>
         <v>14</v>
       </c>
       <c r="N41">
-        <f t="shared" ref="N41:N44" si="6">(J41-J40)/2.5</f>
+        <f t="shared" ref="N41:N44" si="8">(J41-J40)/2.5</f>
         <v>28</v>
       </c>
       <c r="O41">
@@ -9674,11 +12481,11 @@
         <v>250</v>
       </c>
       <c r="Q41">
-        <f>O41*M41</f>
+        <f t="shared" si="4"/>
         <v>1400</v>
       </c>
       <c r="R41">
-        <f>P41*N41</f>
+        <f t="shared" si="4"/>
         <v>7000</v>
       </c>
       <c r="V41">
@@ -9694,15 +12501,15 @@
         <v>-35</v>
       </c>
       <c r="Z41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>35</v>
       </c>
       <c r="AA41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>135</v>
       </c>
       <c r="AB41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AD41">
@@ -9720,11 +12527,11 @@
         <v>250</v>
       </c>
       <c r="AH41">
-        <f>AF41*AD41</f>
+        <f t="shared" si="6"/>
         <v>1000</v>
       </c>
       <c r="AI41">
-        <f>AG41*AE41</f>
+        <f t="shared" si="6"/>
         <v>8000</v>
       </c>
     </row>
@@ -9760,11 +12567,11 @@
         <v>20</v>
       </c>
       <c r="M42">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>4</v>
       </c>
       <c r="N42">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>32</v>
       </c>
       <c r="O42">
@@ -9774,11 +12581,11 @@
         <v>250</v>
       </c>
       <c r="Q42">
-        <f>O42*M42</f>
+        <f t="shared" si="4"/>
         <v>400</v>
       </c>
       <c r="R42">
-        <f>P42*N42</f>
+        <f t="shared" si="4"/>
         <v>8000</v>
       </c>
       <c r="V42">
@@ -9794,15 +12601,15 @@
         <v>-10</v>
       </c>
       <c r="Z42">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>45</v>
       </c>
       <c r="AA42">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>215</v>
       </c>
       <c r="AB42">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>25</v>
       </c>
       <c r="AD42">
@@ -9820,11 +12627,11 @@
         <v>250</v>
       </c>
       <c r="AH42">
-        <f>AF42*AD42</f>
+        <f t="shared" si="6"/>
         <v>1000</v>
       </c>
       <c r="AI42">
-        <f>AG42*AE42</f>
+        <f t="shared" si="6"/>
         <v>8000</v>
       </c>
     </row>
@@ -9854,11 +12661,11 @@
         <v>170</v>
       </c>
       <c r="M43">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>14</v>
       </c>
       <c r="N43">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>28</v>
       </c>
       <c r="O43">
@@ -9868,11 +12675,11 @@
         <v>250</v>
       </c>
       <c r="Q43">
-        <f>O43*M43</f>
+        <f t="shared" si="4"/>
         <v>1400</v>
       </c>
       <c r="R43">
-        <f>P43*N43</f>
+        <f t="shared" si="4"/>
         <v>7000</v>
       </c>
       <c r="V43">
@@ -9888,15 +12695,15 @@
         <v>150</v>
       </c>
       <c r="Z43">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>60</v>
       </c>
       <c r="AA43">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>285</v>
       </c>
       <c r="AB43">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>185</v>
       </c>
       <c r="AD43">
@@ -9914,11 +12721,11 @@
         <v>250</v>
       </c>
       <c r="AH43">
-        <f>AF43*AD43</f>
+        <f t="shared" si="6"/>
         <v>1500</v>
       </c>
       <c r="AI43">
-        <f>AG43*AE43</f>
+        <f t="shared" si="6"/>
         <v>7000</v>
       </c>
     </row>
@@ -9951,11 +12758,11 @@
         <v>10</v>
       </c>
       <c r="M44">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>24</v>
       </c>
       <c r="N44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>28</v>
       </c>
       <c r="O44">
@@ -9965,11 +12772,11 @@
         <v>250</v>
       </c>
       <c r="Q44">
-        <f>O44*M44</f>
+        <f t="shared" si="4"/>
         <v>2400</v>
       </c>
       <c r="R44">
-        <f>P44*N44</f>
+        <f t="shared" si="4"/>
         <v>7000</v>
       </c>
       <c r="V44">
@@ -9985,15 +12792,15 @@
         <v>-15</v>
       </c>
       <c r="Z44">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>75</v>
       </c>
       <c r="AA44">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>365</v>
       </c>
       <c r="AB44">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="AD44">
@@ -10011,11 +12818,11 @@
         <v>250</v>
       </c>
       <c r="AH44">
-        <f>AF44*AD44</f>
+        <f t="shared" si="6"/>
         <v>1500</v>
       </c>
       <c r="AI44">
-        <f>AG44*AE44</f>
+        <f t="shared" si="6"/>
         <v>8000</v>
       </c>
     </row>
@@ -10085,6 +12892,28 @@
       <c r="B46" t="s">
         <v>39</v>
       </c>
+      <c r="L46" t="s">
+        <v>82</v>
+      </c>
+      <c r="M46">
+        <f>_xlfn.STDEV.P(M40:M44)</f>
+        <v>7.0880180586677399</v>
+      </c>
+      <c r="N46">
+        <f>_xlfn.STDEV.P(N40:N44)</f>
+        <v>1.9595917942265426</v>
+      </c>
+      <c r="AC46" t="s">
+        <v>82</v>
+      </c>
+      <c r="AD46">
+        <f>_xlfn.STDEV.P(AD40:AD44)</f>
+        <v>5.4772255750516612</v>
+      </c>
+      <c r="AE46">
+        <f>_xlfn.STDEV.P(AE40:AE44)</f>
+        <v>3.9191835884530848</v>
+      </c>
     </row>
     <row r="47" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
@@ -10093,6 +12922,17 @@
       <c r="B47" t="s">
         <v>41</v>
       </c>
+      <c r="L47" t="s">
+        <v>83</v>
+      </c>
+      <c r="M47">
+        <f>_xlfn.STDEV.P(M40:M44,AD40:AD44)</f>
+        <v>6.3411355449950761</v>
+      </c>
+      <c r="N47">
+        <f>_xlfn.STDEV.P(N40:N44,AE40:AE44)</f>
+        <v>3.1240998703626617</v>
+      </c>
       <c r="Z47" t="s">
         <v>68</v>
       </c>
@@ -10113,14 +12953,15 @@
       <c r="I49">
         <v>0</v>
       </c>
-      <c r="J49">
+      <c r="J49" s="3">
+        <f>I39</f>
         <v>0</v>
       </c>
       <c r="Z49">
         <v>100</v>
       </c>
       <c r="AA49">
-        <f t="shared" ref="AA49:AA53" si="7">Z40</f>
+        <f t="shared" ref="AA49:AA53" si="9">Z40</f>
         <v>25</v>
       </c>
     </row>
@@ -10131,7 +12972,7 @@
       <c r="I50">
         <v>100</v>
       </c>
-      <c r="J50">
+      <c r="J50" s="3">
         <f>I40</f>
         <v>22</v>
       </c>
@@ -10139,7 +12980,7 @@
         <v>200</v>
       </c>
       <c r="AA50">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>35</v>
       </c>
     </row>
@@ -10150,7 +12991,7 @@
       <c r="I51">
         <v>200</v>
       </c>
-      <c r="J51">
+      <c r="J51" s="3">
         <f>I41</f>
         <v>36</v>
       </c>
@@ -10158,7 +12999,7 @@
         <v>300</v>
       </c>
       <c r="AA51">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>45</v>
       </c>
     </row>
@@ -10166,7 +13007,7 @@
       <c r="I52">
         <v>300</v>
       </c>
-      <c r="J52">
+      <c r="J52" s="3">
         <f>I42</f>
         <v>40</v>
       </c>
@@ -10174,7 +13015,7 @@
         <v>400</v>
       </c>
       <c r="AA52">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>60</v>
       </c>
     </row>
@@ -10185,7 +13026,7 @@
       <c r="I53">
         <v>400</v>
       </c>
-      <c r="J53">
+      <c r="J53" s="3">
         <f>I43</f>
         <v>54</v>
       </c>
@@ -10193,7 +13034,7 @@
         <v>500</v>
       </c>
       <c r="AA53">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>75</v>
       </c>
     </row>
@@ -10207,12 +13048,13 @@
       <c r="I54">
         <v>500</v>
       </c>
-      <c r="J54">
+      <c r="J54" s="3">
         <f>I44</f>
         <v>78</v>
       </c>
     </row>
     <row r="55" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="J55" s="3"/>
       <c r="Z55" t="s">
         <v>69</v>
       </c>
@@ -10227,6 +13069,7 @@
       <c r="I56" t="s">
         <v>69</v>
       </c>
+      <c r="J56" s="3"/>
       <c r="Z56">
         <v>0</v>
       </c>
@@ -10251,14 +13094,15 @@
       <c r="I57">
         <v>0</v>
       </c>
-      <c r="J57">
+      <c r="J57" s="3">
+        <f>J39</f>
         <v>0</v>
       </c>
       <c r="Z57">
         <v>250</v>
       </c>
       <c r="AA57">
-        <f t="shared" ref="AA57:AA61" si="8">AA40</f>
+        <f t="shared" ref="AA57:AA61" si="10">AA40</f>
         <v>55</v>
       </c>
     </row>
@@ -10278,7 +13122,7 @@
       <c r="I58">
         <v>250</v>
       </c>
-      <c r="J58">
+      <c r="J58" s="3">
         <f>J40</f>
         <v>65</v>
       </c>
@@ -10286,7 +13130,7 @@
         <v>500</v>
       </c>
       <c r="AA58">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>135</v>
       </c>
     </row>
@@ -10294,7 +13138,7 @@
       <c r="I59">
         <v>500</v>
       </c>
-      <c r="J59">
+      <c r="J59" s="3">
         <f>J41</f>
         <v>135</v>
       </c>
@@ -10302,7 +13146,7 @@
         <v>750</v>
       </c>
       <c r="AA59">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>215</v>
       </c>
     </row>
@@ -10313,7 +13157,7 @@
       <c r="I60">
         <v>750</v>
       </c>
-      <c r="J60">
+      <c r="J60" s="3">
         <f>J42</f>
         <v>215</v>
       </c>
@@ -10321,7 +13165,7 @@
         <v>1000</v>
       </c>
       <c r="AA60">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>285</v>
       </c>
     </row>
@@ -10341,7 +13185,7 @@
       <c r="I61">
         <v>1000</v>
       </c>
-      <c r="J61">
+      <c r="J61" s="3">
         <f>J43</f>
         <v>285</v>
       </c>
@@ -10349,7 +13193,7 @@
         <v>1250</v>
       </c>
       <c r="AA61">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>365</v>
       </c>
     </row>
@@ -10363,7 +13207,7 @@
       <c r="I62">
         <v>1250</v>
       </c>
-      <c r="J62">
+      <c r="J62" s="3">
         <f>J44</f>
         <v>355</v>
       </c>
@@ -10447,189 +13291,891 @@
       </c>
     </row>
     <row r="69" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="I69">
+      <c r="I69" s="4">
         <f>J69/$T$45*100</f>
         <v>0</v>
       </c>
-      <c r="J69">
-        <f>K39</f>
+      <c r="J69" s="4">
+        <f t="shared" ref="J69:J74" si="11">K39</f>
         <v>0</v>
       </c>
+      <c r="K69" s="4"/>
       <c r="L69" t="e">
-        <f>K69/I69</f>
+        <f t="shared" ref="L69:L74" si="12">K69/I69</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z69">
+      <c r="Z69" s="4">
         <f>AA69/$AK$45*100</f>
         <v>0</v>
       </c>
-      <c r="AA69">
-        <f>AB39</f>
+      <c r="AA69" s="4">
+        <f t="shared" ref="AA69:AA74" si="13">AB39</f>
         <v>0</v>
       </c>
+      <c r="AB69" s="4"/>
       <c r="AC69" t="e">
-        <f>AB69/Z69</f>
+        <f t="shared" ref="AC69:AC74" si="14">AB69/Z69</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="70" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="I70" s="3">
-        <f t="shared" ref="I70:I74" si="9">J70/$T$45*100</f>
+      <c r="I70" s="4">
+        <f t="shared" ref="I70:I74" si="15">J70/$T$45*100</f>
         <v>525.40415704387988</v>
       </c>
-      <c r="J70">
-        <f>K40</f>
+      <c r="J70" s="4">
+        <f t="shared" si="11"/>
         <v>130</v>
       </c>
-      <c r="K70">
+      <c r="K70" s="4">
         <v>500</v>
       </c>
       <c r="L70">
-        <f>K70/I70</f>
+        <f t="shared" si="12"/>
         <v>0.95164835164835171</v>
       </c>
-      <c r="Z70" s="3">
-        <f t="shared" ref="Z70:Z74" si="10">AA70/$AK$45*100</f>
+      <c r="Z70" s="4">
+        <f t="shared" ref="Z70:Z74" si="16">AA70/$AK$45*100</f>
         <v>517.04545454545462</v>
       </c>
-      <c r="AA70">
-        <f>AB40</f>
+      <c r="AA70" s="4">
+        <f t="shared" si="13"/>
         <v>130</v>
       </c>
-      <c r="AB70">
+      <c r="AB70" s="4">
         <v>500</v>
       </c>
       <c r="AC70">
-        <f>AB70/Z70</f>
+        <f t="shared" si="14"/>
         <v>0.96703296703296693</v>
       </c>
     </row>
     <row r="71" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="I71" s="3">
-        <f t="shared" si="9"/>
+      <c r="I71" s="4">
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="J71">
-        <f>K41</f>
+      <c r="J71" s="4">
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="K71">
+      <c r="K71" s="4">
         <v>0</v>
       </c>
       <c r="L71" t="e">
-        <f>K71/I71</f>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z71" s="3">
-        <f t="shared" si="10"/>
+      <c r="Z71" s="4">
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AA71">
-        <f>AB41</f>
+      <c r="AA71" s="4">
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AB71">
+      <c r="AB71" s="4">
         <v>0</v>
       </c>
       <c r="AC71" t="e">
-        <f>AB71/Z71</f>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="72" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="I72" s="3">
-        <f t="shared" si="9"/>
+      <c r="I72" s="4">
+        <f t="shared" si="15"/>
         <v>80.831408775981515</v>
       </c>
-      <c r="J72">
-        <f>K42</f>
+      <c r="J72" s="4">
+        <f t="shared" si="11"/>
         <v>20</v>
       </c>
-      <c r="K72">
-        <v>100</v>
+      <c r="K72" s="4">
+        <v>75</v>
       </c>
       <c r="L72">
-        <f>K72/I72</f>
-        <v>1.2371428571428573</v>
-      </c>
-      <c r="Z72" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
+        <v>0.92785714285714294</v>
+      </c>
+      <c r="Z72" s="4">
+        <f t="shared" si="16"/>
         <v>99.431818181818187</v>
       </c>
-      <c r="AA72">
-        <f>AB42</f>
+      <c r="AA72" s="4">
+        <f t="shared" si="13"/>
         <v>25</v>
       </c>
-      <c r="AB72">
-        <v>100</v>
+      <c r="AB72" s="4">
+        <v>75</v>
       </c>
       <c r="AC72">
-        <f>AB72/Z72</f>
-        <v>1.0057142857142856</v>
+        <f t="shared" si="14"/>
+        <v>0.75428571428571423</v>
       </c>
     </row>
     <row r="73" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="I73" s="3">
-        <f t="shared" si="9"/>
+      <c r="I73" s="4">
+        <f t="shared" si="15"/>
         <v>687.06697459584291</v>
       </c>
-      <c r="J73">
-        <f>K43</f>
+      <c r="J73" s="4">
+        <f t="shared" si="11"/>
         <v>170</v>
       </c>
-      <c r="K73">
+      <c r="K73" s="4">
         <v>700</v>
       </c>
       <c r="L73">
-        <f>K73/I73</f>
+        <f t="shared" si="12"/>
         <v>1.0188235294117647</v>
       </c>
-      <c r="Z73" s="3">
-        <f t="shared" si="10"/>
+      <c r="Z73" s="4">
+        <f t="shared" si="16"/>
         <v>735.79545454545462</v>
       </c>
-      <c r="AA73">
-        <f>AB43</f>
+      <c r="AA73" s="4">
+        <f t="shared" si="13"/>
         <v>185</v>
       </c>
-      <c r="AB73">
+      <c r="AB73" s="4">
         <v>700</v>
       </c>
       <c r="AC73">
-        <f>AB73/Z73</f>
+        <f t="shared" si="14"/>
         <v>0.95135135135135129</v>
       </c>
     </row>
     <row r="74" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="I74" s="3">
-        <f t="shared" si="9"/>
+      <c r="I74" s="4">
+        <f t="shared" si="15"/>
         <v>40.415704387990758</v>
       </c>
-      <c r="J74">
-        <f>K44</f>
+      <c r="J74" s="4">
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
-      <c r="K74">
+      <c r="K74" s="4">
         <v>50</v>
       </c>
       <c r="L74">
-        <f>K74/I74</f>
+        <f t="shared" si="12"/>
         <v>1.2371428571428573</v>
       </c>
-      <c r="Z74" s="3">
-        <f t="shared" si="10"/>
+      <c r="Z74" s="4">
+        <f t="shared" si="16"/>
         <v>79.545454545454547</v>
       </c>
-      <c r="AA74">
-        <f>AB44</f>
+      <c r="AA74" s="4">
+        <f t="shared" si="13"/>
         <v>20</v>
       </c>
-      <c r="AB74">
+      <c r="AB74" s="4">
         <v>50</v>
       </c>
       <c r="AC74">
-        <f>AB74/Z74</f>
+        <f t="shared" si="14"/>
         <v>0.62857142857142856</v>
+      </c>
+    </row>
+    <row r="115" spans="5:20" x14ac:dyDescent="0.25">
+      <c r="F115" t="s">
+        <v>71</v>
+      </c>
+      <c r="I115" t="s">
+        <v>73</v>
+      </c>
+      <c r="M115" t="s">
+        <v>74</v>
+      </c>
+      <c r="O115" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q115" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="116" spans="5:20" x14ac:dyDescent="0.25">
+      <c r="F116">
+        <v>100</v>
+      </c>
+      <c r="G116">
+        <v>250</v>
+      </c>
+      <c r="H116" t="s">
+        <v>34</v>
+      </c>
+      <c r="I116">
+        <v>100</v>
+      </c>
+      <c r="J116">
+        <v>250</v>
+      </c>
+      <c r="K116" t="s">
+        <v>34</v>
+      </c>
+      <c r="M116">
+        <v>100</v>
+      </c>
+      <c r="N116">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="117" spans="5:20" x14ac:dyDescent="0.25">
+      <c r="E117">
+        <v>0</v>
+      </c>
+      <c r="F117">
+        <v>-100</v>
+      </c>
+      <c r="G117">
+        <v>-20</v>
+      </c>
+      <c r="H117">
+        <v>-50</v>
+      </c>
+      <c r="I117">
+        <f>F117-$F$117</f>
+        <v>0</v>
+      </c>
+      <c r="J117">
+        <f>G117-$G$117</f>
+        <v>0</v>
+      </c>
+      <c r="K117">
+        <f>H117-$H$117</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="5:20" x14ac:dyDescent="0.25">
+      <c r="E118">
+        <v>1</v>
+      </c>
+      <c r="F118">
+        <v>-80</v>
+      </c>
+      <c r="G118">
+        <v>70</v>
+      </c>
+      <c r="H118">
+        <v>85</v>
+      </c>
+      <c r="I118">
+        <f t="shared" ref="I118:I122" si="17">F118-$F$117</f>
+        <v>20</v>
+      </c>
+      <c r="J118">
+        <f t="shared" ref="J118:J122" si="18">G118-$G$117</f>
+        <v>90</v>
+      </c>
+      <c r="K118">
+        <f t="shared" ref="K118:K122" si="19">H118-$H$117</f>
+        <v>135</v>
+      </c>
+      <c r="M118">
+        <f>I118-I117</f>
+        <v>20</v>
+      </c>
+      <c r="N118">
+        <f>(J118-J117)/2.5</f>
+        <v>36</v>
+      </c>
+      <c r="O118">
+        <v>100</v>
+      </c>
+      <c r="P118">
+        <v>250</v>
+      </c>
+      <c r="Q118">
+        <f t="shared" ref="Q118:Q122" si="20">O118*M118</f>
+        <v>2000</v>
+      </c>
+      <c r="R118">
+        <f t="shared" ref="R118:R122" si="21">P118*N118</f>
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="119" spans="5:20" x14ac:dyDescent="0.25">
+      <c r="E119">
+        <v>2</v>
+      </c>
+      <c r="F119">
+        <v>-70</v>
+      </c>
+      <c r="G119">
+        <v>140</v>
+      </c>
+      <c r="H119">
+        <v>-50</v>
+      </c>
+      <c r="I119">
+        <f t="shared" si="17"/>
+        <v>30</v>
+      </c>
+      <c r="J119">
+        <f t="shared" si="18"/>
+        <v>160</v>
+      </c>
+      <c r="K119">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="M119">
+        <f t="shared" ref="M119:M122" si="22">I119-I118</f>
+        <v>10</v>
+      </c>
+      <c r="N119">
+        <f t="shared" ref="N119:N122" si="23">(J119-J118)/2.5</f>
+        <v>28</v>
+      </c>
+      <c r="O119">
+        <v>100</v>
+      </c>
+      <c r="P119">
+        <v>250</v>
+      </c>
+      <c r="Q119">
+        <f t="shared" si="20"/>
+        <v>1000</v>
+      </c>
+      <c r="R119">
+        <f t="shared" si="21"/>
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="120" spans="5:20" x14ac:dyDescent="0.25">
+      <c r="E120">
+        <v>3</v>
+      </c>
+      <c r="F120">
+        <v>-60</v>
+      </c>
+      <c r="G120">
+        <v>220</v>
+      </c>
+      <c r="H120">
+        <v>-35</v>
+      </c>
+      <c r="I120">
+        <f t="shared" si="17"/>
+        <v>40</v>
+      </c>
+      <c r="J120">
+        <f t="shared" si="18"/>
+        <v>240</v>
+      </c>
+      <c r="K120">
+        <f t="shared" si="19"/>
+        <v>15</v>
+      </c>
+      <c r="M120">
+        <f t="shared" si="22"/>
+        <v>10</v>
+      </c>
+      <c r="N120">
+        <f t="shared" si="23"/>
+        <v>32</v>
+      </c>
+      <c r="O120">
+        <v>100</v>
+      </c>
+      <c r="P120">
+        <v>250</v>
+      </c>
+      <c r="Q120">
+        <f t="shared" si="20"/>
+        <v>1000</v>
+      </c>
+      <c r="R120">
+        <f t="shared" si="21"/>
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="121" spans="5:20" x14ac:dyDescent="0.25">
+      <c r="E121">
+        <v>4</v>
+      </c>
+      <c r="F121">
+        <v>-40</v>
+      </c>
+      <c r="G121">
+        <v>300</v>
+      </c>
+      <c r="H121">
+        <v>130</v>
+      </c>
+      <c r="I121">
+        <f t="shared" si="17"/>
+        <v>60</v>
+      </c>
+      <c r="J121">
+        <f t="shared" si="18"/>
+        <v>320</v>
+      </c>
+      <c r="K121">
+        <f t="shared" si="19"/>
+        <v>180</v>
+      </c>
+      <c r="M121">
+        <f t="shared" si="22"/>
+        <v>20</v>
+      </c>
+      <c r="N121">
+        <f t="shared" si="23"/>
+        <v>32</v>
+      </c>
+      <c r="O121">
+        <v>100</v>
+      </c>
+      <c r="P121">
+        <v>250</v>
+      </c>
+      <c r="Q121">
+        <f t="shared" si="20"/>
+        <v>2000</v>
+      </c>
+      <c r="R121">
+        <f t="shared" si="21"/>
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="122" spans="5:20" x14ac:dyDescent="0.25">
+      <c r="E122">
+        <v>5</v>
+      </c>
+      <c r="F122">
+        <v>-20</v>
+      </c>
+      <c r="G122">
+        <v>370</v>
+      </c>
+      <c r="H122">
+        <v>-40</v>
+      </c>
+      <c r="I122">
+        <f t="shared" si="17"/>
+        <v>80</v>
+      </c>
+      <c r="J122">
+        <f t="shared" si="18"/>
+        <v>390</v>
+      </c>
+      <c r="K122">
+        <f t="shared" si="19"/>
+        <v>10</v>
+      </c>
+      <c r="M122">
+        <f t="shared" si="22"/>
+        <v>20</v>
+      </c>
+      <c r="N122">
+        <f t="shared" si="23"/>
+        <v>28</v>
+      </c>
+      <c r="O122">
+        <v>100</v>
+      </c>
+      <c r="P122">
+        <v>250</v>
+      </c>
+      <c r="Q122">
+        <f t="shared" si="20"/>
+        <v>2000</v>
+      </c>
+      <c r="R122">
+        <f t="shared" si="21"/>
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="123" spans="5:20" x14ac:dyDescent="0.25">
+      <c r="E123" t="s">
+        <v>67</v>
+      </c>
+      <c r="F123">
+        <f>(F122-F117)/5</f>
+        <v>16</v>
+      </c>
+      <c r="G123">
+        <f>(G122-G117)/5</f>
+        <v>78</v>
+      </c>
+      <c r="H123">
+        <f>(H122-H117)/5</f>
+        <v>2</v>
+      </c>
+      <c r="L123" t="s">
+        <v>72</v>
+      </c>
+      <c r="M123">
+        <f>AVERAGE(M118:M122)</f>
+        <v>16</v>
+      </c>
+      <c r="N123">
+        <f>AVERAGE(N118:N122)</f>
+        <v>31.2</v>
+      </c>
+      <c r="S123" t="s">
+        <v>77</v>
+      </c>
+      <c r="T123">
+        <f>SUM(Q118:R122)/SUM(O118:P122)</f>
+        <v>26.857142857142858</v>
+      </c>
+    </row>
+    <row r="124" spans="5:20" x14ac:dyDescent="0.25">
+      <c r="L124" t="s">
+        <v>82</v>
+      </c>
+      <c r="M124">
+        <f>_xlfn.STDEV.P(M118:M122)</f>
+        <v>4.8989794855663558</v>
+      </c>
+      <c r="N124">
+        <f>_xlfn.STDEV.P(N118:N122)</f>
+        <v>2.9933259094191529</v>
+      </c>
+    </row>
+    <row r="125" spans="5:20" x14ac:dyDescent="0.25">
+      <c r="L125" t="s">
+        <v>84</v>
+      </c>
+      <c r="M125">
+        <f>M124/M47</f>
+        <v>0.77257132430058473</v>
+      </c>
+      <c r="N125">
+        <f>N124/N47</f>
+        <v>0.95814027516081679</v>
+      </c>
+    </row>
+    <row r="126" spans="5:20" x14ac:dyDescent="0.25">
+      <c r="I126" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="127" spans="5:20" x14ac:dyDescent="0.25">
+      <c r="I127">
+        <v>0</v>
+      </c>
+      <c r="J127">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="5:20" x14ac:dyDescent="0.25">
+      <c r="I128">
+        <v>100</v>
+      </c>
+      <c r="J128">
+        <f>I118</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="129" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I129">
+        <v>200</v>
+      </c>
+      <c r="J129">
+        <f>I119</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="130" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I130">
+        <v>300</v>
+      </c>
+      <c r="J130">
+        <f>I120</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="131" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I131">
+        <v>400</v>
+      </c>
+      <c r="J131">
+        <f>I121</f>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="132" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I132">
+        <v>500</v>
+      </c>
+      <c r="J132">
+        <f>I122</f>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="134" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I134" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="135" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I135">
+        <v>0</v>
+      </c>
+      <c r="J135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I136">
+        <v>250</v>
+      </c>
+      <c r="J136">
+        <f>J118</f>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="137" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I137">
+        <v>500</v>
+      </c>
+      <c r="J137">
+        <f>J119</f>
+        <v>160</v>
+      </c>
+    </row>
+    <row r="138" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I138">
+        <v>750</v>
+      </c>
+      <c r="J138">
+        <f>J120</f>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="139" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I139">
+        <v>1000</v>
+      </c>
+      <c r="J139">
+        <f>J121</f>
+        <v>320</v>
+      </c>
+    </row>
+    <row r="140" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I140">
+        <v>1250</v>
+      </c>
+      <c r="J140">
+        <f>J122</f>
+        <v>390</v>
+      </c>
+    </row>
+    <row r="142" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I142" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="143" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I143">
+        <v>0</v>
+      </c>
+      <c r="J143">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I144">
+        <v>1500</v>
+      </c>
+      <c r="J144">
+        <f>I144*T123/100</f>
+        <v>402.85714285714289</v>
+      </c>
+    </row>
+    <row r="146" spans="8:18" x14ac:dyDescent="0.25">
+      <c r="H146" t="s">
+        <v>85</v>
+      </c>
+      <c r="I146" t="s">
+        <v>34</v>
+      </c>
+      <c r="K146" t="s">
+        <v>80</v>
+      </c>
+      <c r="O146" t="s">
+        <v>86</v>
+      </c>
+      <c r="P146" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q146" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="147" spans="8:18" x14ac:dyDescent="0.25">
+      <c r="I147" s="4">
+        <f>J147/$T$123*100</f>
+        <v>0</v>
+      </c>
+      <c r="J147" s="4">
+        <f t="shared" ref="J147:J152" si="24">K117</f>
+        <v>0</v>
+      </c>
+      <c r="K147" s="4"/>
+      <c r="L147" t="e">
+        <f t="shared" ref="L147:L152" si="25">K147/I147</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P147" s="4">
+        <f>I69</f>
+        <v>0</v>
+      </c>
+      <c r="Q147" s="4">
+        <f>Z69</f>
+        <v>0</v>
+      </c>
+      <c r="R147" s="4">
+        <f>AVERAGE(I69,Z69)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="8:18" x14ac:dyDescent="0.25">
+      <c r="I148" s="4">
+        <f t="shared" ref="I148:I152" si="26">J148/$T$123*100</f>
+        <v>502.65957446808505</v>
+      </c>
+      <c r="J148" s="4">
+        <f t="shared" si="24"/>
+        <v>135</v>
+      </c>
+      <c r="K148" s="4">
+        <v>500</v>
+      </c>
+      <c r="L148">
+        <f t="shared" si="25"/>
+        <v>0.99470899470899476</v>
+      </c>
+      <c r="P148" s="4">
+        <f t="shared" ref="P148:P152" si="27">I70</f>
+        <v>525.40415704387988</v>
+      </c>
+      <c r="Q148" s="4">
+        <f t="shared" ref="Q148:Q152" si="28">Z70</f>
+        <v>517.04545454545462</v>
+      </c>
+      <c r="R148" s="4">
+        <f>AVERAGE(I70,Z70)</f>
+        <v>521.22480579466719</v>
+      </c>
+    </row>
+    <row r="149" spans="8:18" x14ac:dyDescent="0.25">
+      <c r="I149" s="4">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="J149" s="4">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="K149" s="4">
+        <v>0</v>
+      </c>
+      <c r="L149" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P149" s="4">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="Q149" s="4">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="R149" s="4">
+        <f>AVERAGE(I71,Z71)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="8:18" x14ac:dyDescent="0.25">
+      <c r="I150" s="4">
+        <f t="shared" si="26"/>
+        <v>55.851063829787229</v>
+      </c>
+      <c r="J150" s="4">
+        <f t="shared" si="24"/>
+        <v>15</v>
+      </c>
+      <c r="K150" s="4">
+        <v>75</v>
+      </c>
+      <c r="L150">
+        <f t="shared" si="25"/>
+        <v>1.342857142857143</v>
+      </c>
+      <c r="P150" s="4">
+        <f t="shared" si="27"/>
+        <v>80.831408775981515</v>
+      </c>
+      <c r="Q150" s="4">
+        <f t="shared" si="28"/>
+        <v>99.431818181818187</v>
+      </c>
+      <c r="R150" s="4">
+        <f>AVERAGE(I72,Z72)</f>
+        <v>90.131613478899851</v>
+      </c>
+    </row>
+    <row r="151" spans="8:18" x14ac:dyDescent="0.25">
+      <c r="I151" s="4">
+        <f t="shared" si="26"/>
+        <v>670.21276595744678</v>
+      </c>
+      <c r="J151" s="4">
+        <f t="shared" si="24"/>
+        <v>180</v>
+      </c>
+      <c r="K151" s="4">
+        <v>700</v>
+      </c>
+      <c r="L151">
+        <f t="shared" si="25"/>
+        <v>1.0444444444444445</v>
+      </c>
+      <c r="P151" s="4">
+        <f t="shared" si="27"/>
+        <v>687.06697459584291</v>
+      </c>
+      <c r="Q151" s="4">
+        <f t="shared" si="28"/>
+        <v>735.79545454545462</v>
+      </c>
+      <c r="R151" s="4">
+        <f>AVERAGE(I73,Z73)</f>
+        <v>711.43121457064876</v>
+      </c>
+    </row>
+    <row r="152" spans="8:18" x14ac:dyDescent="0.25">
+      <c r="I152" s="4">
+        <f t="shared" si="26"/>
+        <v>37.234042553191486</v>
+      </c>
+      <c r="J152" s="4">
+        <f t="shared" si="24"/>
+        <v>10</v>
+      </c>
+      <c r="K152" s="4">
+        <v>50</v>
+      </c>
+      <c r="L152">
+        <f t="shared" si="25"/>
+        <v>1.342857142857143</v>
+      </c>
+      <c r="P152" s="4">
+        <f t="shared" si="27"/>
+        <v>40.415704387990758</v>
+      </c>
+      <c r="Q152" s="4">
+        <f t="shared" si="28"/>
+        <v>79.545454545454547</v>
+      </c>
+      <c r="R152" s="4">
+        <f>AVERAGE(I74,Z74)</f>
+        <v>59.980579466722652</v>
       </c>
     </row>
   </sheetData>
